--- a/inventario_operaciones.xlsx
+++ b/inventario_operaciones.xlsx
@@ -673,19 +673,19 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KM041304</t>
+          <t>K020506</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DROPS PINK GOLD</t>
+          <t>MASCARILLA FACIAL DE CHOCOLATE KABA</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>786</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>178.6259541984733</v>
+        <v>138.7786259541985</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -701,19 +701,19 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>K020506</t>
+          <t>KM041304</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MASCARILLA FACIAL DE CHOCOLATE KABA</t>
+          <t>DROPS PINK GOLD</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>786</v>
       </c>
       <c r="D11" t="n">
-        <v>138.7786259541985</v>
+        <v>178.6259541984733</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -729,19 +729,19 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>KM041301</t>
+          <t>KM041302</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DROPS CHAMPAGNE GOLD</t>
+          <t>DROPS CHAMPAGNE SILVER</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>369</v>
+        <v>778</v>
       </c>
       <c r="D12" t="n">
-        <v>760.8778625954199</v>
+        <v>192.7099236641222</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -757,19 +757,19 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>KM041302</t>
+          <t>KM041301</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DROPS CHAMPAGNE SILVER</t>
+          <t>DROPS CHAMPAGNE GOLD</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>778</v>
+        <v>369</v>
       </c>
       <c r="D13" t="n">
-        <v>192.7099236641222</v>
+        <v>760.8778625954199</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -869,19 +869,19 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>K020604</t>
+          <t>KM041106</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SERUM VITAMINA C KABA</t>
+          <t>CORRECTOR DE OJERAS MIEL</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>396</v>
+        <v>873</v>
       </c>
       <c r="D17" t="n">
-        <v>1436.221374045801</v>
+        <v>1522.786259541985</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -897,18 +897,20 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K010304USA</t>
+          <t>KM041308</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HAIR TONIC KABA</t>
+          <t>ILUMINADOR LIQUIDO PRETTY GIRL</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>41</v>
-      </c>
-      <c r="D18" t="inlineStr"/>
+        <v>147</v>
+      </c>
+      <c r="D18" t="n">
+        <v>148.3969465648855</v>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>PRODUCTO MANUFACTURADO</t>
@@ -923,19 +925,19 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>KM041106</t>
+          <t>K020604</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CORRECTOR DE OJERAS MIEL</t>
+          <t>SERUM VITAMINA C KABA</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>873</v>
+        <v>396</v>
       </c>
       <c r="D19" t="n">
-        <v>1522.786259541985</v>
+        <v>1436.221374045801</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -951,20 +953,18 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KM041308</t>
+          <t>K010304USA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ILUMINADOR LIQUIDO PRETTY GIRL</t>
+          <t>HAIR TONIC KABA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>147</v>
-      </c>
-      <c r="D20" t="n">
-        <v>148.3969465648855</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>PRODUCTO MANUFACTURADO</t>
@@ -1231,19 +1231,19 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>D030605</t>
+          <t>K010102</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MINI REGENERADOR DE ALMENDRAS DLUCHI</t>
+          <t>SHAMPOO KIDS KABA</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>348</v>
+        <v>53</v>
       </c>
       <c r="D30" t="n">
-        <v>2111.564885496183</v>
+        <v>2141.106870229008</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1259,19 +1259,19 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>K010102</t>
+          <t>D030605</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SHAMPOO KIDS KABA</t>
+          <t>MINI REGENERADOR DE ALMENDRAS DLUCHI</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>53</v>
+        <v>348</v>
       </c>
       <c r="D31" t="n">
-        <v>2141.106870229008</v>
+        <v>2111.564885496183</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1287,19 +1287,19 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>KM041314</t>
+          <t>KM041312</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>RUBOR LIQUIDO MARGARITA</t>
+          <t>RUBOR LIQUIDO SUNRISE</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>866</v>
+        <v>913</v>
       </c>
       <c r="D32" t="n">
-        <v>106.8320610687023</v>
+        <v>98.587786259542</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1315,16 +1315,16 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>KM041311</t>
+          <t>KM041315</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>RUBOR LIQUIDO MARTINI</t>
+          <t>RUBOR LIQUIDO COCO LOCO</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>870</v>
+        <v>853</v>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
@@ -1341,19 +1341,19 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>KM041312</t>
+          <t>KM041313</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>RUBOR LIQUIDO SUNRISE</t>
+          <t>RUBOR LIQUIDO MANHATTAN</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>913</v>
+        <v>507</v>
       </c>
       <c r="D34" t="n">
-        <v>98.587786259542</v>
+        <v>102.0229007633588</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1369,18 +1369,20 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>KM041315</t>
+          <t>KM041314</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>RUBOR LIQUIDO COCO LOCO</t>
+          <t>RUBOR LIQUIDO MARGARITA</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>853</v>
-      </c>
-      <c r="D35" t="inlineStr"/>
+        <v>866</v>
+      </c>
+      <c r="D35" t="n">
+        <v>106.8320610687023</v>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>PRODUCTO MANUFACTURADO</t>
@@ -1395,20 +1397,18 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>KM041313</t>
+          <t>KM041311</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RUBOR LIQUIDO MANHATTAN</t>
+          <t>RUBOR LIQUIDO MARTINI</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>507</v>
-      </c>
-      <c r="D36" t="n">
-        <v>102.0229007633588</v>
-      </c>
+        <v>870</v>
+      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
           <t>PRODUCTO MANUFACTURADO</t>
@@ -2521,19 +2521,19 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>KITK0110</t>
+          <t>KITK0206</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>KIT SOS KABA</t>
+          <t>KIT RUTINA AM KABA</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="D77" t="n">
-        <v>56.5648854961832</v>
+        <v>34.69465648854962</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2549,19 +2549,19 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>KITK0206</t>
+          <t>KITK0110</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>KIT RUTINA AM KABA</t>
+          <t>KIT SOS KABA</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D78" t="n">
-        <v>34.69465648854962</v>
+        <v>56.5648854961832</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2745,19 +2745,19 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>CAJAEMPRENDEDORA</t>
+          <t>D031007</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CAJA EMPRENDEDORA</t>
+          <t>CREMA AUTOBRONCEADORA DLUCHI</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>4</v>
+        <v>136</v>
       </c>
       <c r="D85" t="n">
-        <v>15.11450381679389</v>
+        <v>4299.732824427481</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -2773,19 +2773,19 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>D031007</t>
+          <t>CAJAEMPRENDEDORA</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CREMA AUTOBRONCEADORA DLUCHI</t>
+          <t>CAJA EMPRENDEDORA</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>136</v>
+        <v>4</v>
       </c>
       <c r="D86" t="n">
-        <v>4299.732824427481</v>
+        <v>15.11450381679389</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -2857,19 +2857,19 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>KITD0305</t>
+          <t>KITD0307</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>KIT BRONCEOPERF VAR COCO DLUCHI</t>
+          <t>KIT DUO BRONCEADORES DLUCHI</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="D89" t="n">
-        <v>47.06106870229008</v>
+        <v>36.64122137404581</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -2885,19 +2885,19 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>KITD0307</t>
+          <t>KITD0305</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>KIT DUO BRONCEADORES DLUCHI</t>
+          <t>KIT BRONCEOPERF VAR COCO DLUCHI</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="D90" t="n">
-        <v>36.64122137404581</v>
+        <v>47.06106870229008</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3025,19 +3025,19 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>K020702</t>
+          <t>K010405</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>LOCION ASTRINGENTE KABA</t>
+          <t>PERFUME PARA EL CABELLO EXITOSA KABA</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>263</v>
+        <v>122</v>
       </c>
       <c r="D95" t="n">
-        <v>8045.038167938931</v>
+        <v>1701.068702290076</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3053,19 +3053,19 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>K030901</t>
+          <t>K020702</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>CREMA CORPORAL ACLARANTE KABA</t>
+          <t>LOCION ASTRINGENTE KABA</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>645</v>
+        <v>263</v>
       </c>
       <c r="D96" t="n">
-        <v>11863.1679389313</v>
+        <v>8045.038167938931</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3081,19 +3081,19 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>K010405</t>
+          <t>K030901</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PERFUME PARA EL CABELLO EXITOSA KABA</t>
+          <t>CREMA CORPORAL ACLARANTE KABA</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>122</v>
+        <v>645</v>
       </c>
       <c r="D97" t="n">
-        <v>1701.068702290076</v>
+        <v>11863.1679389313</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3109,19 +3109,19 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>K010305</t>
+          <t>D030603</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>TRATAMIENTO REPARACION SOS KABA</t>
+          <t>MANTEQUILLA CORPORAL DLUCHI</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D98" t="n">
-        <v>1825.763358778626</v>
+        <v>6729.73282442748</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3137,19 +3137,19 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>D030603</t>
+          <t>K010305</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>MANTEQUILLA CORPORAL DLUCHI</t>
+          <t>TRATAMIENTO REPARACION SOS KABA</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D99" t="n">
-        <v>6729.73282442748</v>
+        <v>1825.763358778626</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3333,18 +3333,20 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>KITE0102</t>
+          <t>KITR0106</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>KIT NUTRICIÓN Y CRECIMIENTO</t>
+          <t>KIT DUO CABELLO SECO LA RECETA</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>8</v>
-      </c>
-      <c r="D106" t="inlineStr"/>
+        <v>31</v>
+      </c>
+      <c r="D106" t="n">
+        <v>41.33587786259542</v>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>PRODUCTO MANUFACTURADO</t>
@@ -3359,20 +3361,18 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>KITR0106</t>
+          <t>KITE0102</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>KIT DUO CABELLO SECO LA RECETA</t>
+          <t>KIT NUTRICIÓN Y CRECIMIENTO</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>31</v>
-      </c>
-      <c r="D107" t="n">
-        <v>41.33587786259542</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
           <t>PRODUCTO MANUFACTURADO</t>
@@ -3469,18 +3469,20 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>KITD0911</t>
+          <t>KITKR0101</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>KIT PIEL CANELA OSCURO</t>
+          <t>KIT CAPILAR KABA + SHAMPO ANTICASPA</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>12</v>
-      </c>
-      <c r="D111" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="D111" t="n">
+        <v>15.11450381679389</v>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>PRODUCTO MANUFACTURADO</t>
@@ -3495,20 +3497,18 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>KITKR0101</t>
+          <t>KITD0911</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>KIT CAPILAR KABA + SHAMPO ANTICASPA</t>
+          <t>KIT PIEL CANELA OSCURO</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>13</v>
-      </c>
-      <c r="D112" t="n">
-        <v>15.11450381679389</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
           <t>PRODUCTO MANUFACTURADO</t>
@@ -3633,19 +3633,19 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>K010403</t>
+          <t>KM041205</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>PERFUME PARA EL CABELLO SOÑADORA KABA</t>
+          <t>LIP GLOSS VOLUMINIZANTE ROSE VELVET</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>55</v>
+        <v>677</v>
       </c>
       <c r="D117" t="n">
-        <v>1100.954198473282</v>
+        <v>1443.435114503817</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -3661,19 +3661,19 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>K010402</t>
+          <t>K010403</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>PERFUME PARA EL CABELLO CONFIDENTE KABA</t>
+          <t>PERFUME PARA EL CABELLO SOÑADORA KABA</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>148</v>
+        <v>55</v>
       </c>
       <c r="D118" t="n">
-        <v>1163.473282442748</v>
+        <v>1100.954198473282</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -3689,19 +3689,19 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>KM041205</t>
+          <t>K010402</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>LIP GLOSS VOLUMINIZANTE ROSE VELVET</t>
+          <t>PERFUME PARA EL CABELLO CONFIDENTE KABA</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>677</v>
+        <v>148</v>
       </c>
       <c r="D119" t="n">
-        <v>1443.435114503817</v>
+        <v>1163.473282442748</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -3801,19 +3801,19 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>KM041202</t>
+          <t>KM041105</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>LIP GLOSS GOLDEN HOUR</t>
+          <t>CORRECTOR DE OJERAS MACADAMIA</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>726</v>
+        <v>706</v>
       </c>
       <c r="D123" t="n">
-        <v>171.412213740458</v>
+        <v>347.2900763358779</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -3857,19 +3857,19 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>KM041105</t>
+          <t>KM041202</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>CORRECTOR DE OJERAS MACADAMIA</t>
+          <t>LIP GLOSS GOLDEN HOUR</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>706</v>
+        <v>726</v>
       </c>
       <c r="D125" t="n">
-        <v>347.2900763358779</v>
+        <v>171.412213740458</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -3997,19 +3997,19 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>KITK0201</t>
+          <t>KITK0105</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>KIT DE EMERGENCIA FACIAL KABA</t>
+          <t>KIT DE PERFUMES PARA CABELLO KABA</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="D130" t="n">
-        <v>95.95419847328245</v>
+        <v>20.72519083969465</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4025,19 +4025,19 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>KITR0101</t>
+          <t>KITK0201</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>KIT ADIOS GRASA LA RECETA</t>
+          <t>KIT DE EMERGENCIA FACIAL KABA</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="D131" t="n">
-        <v>21.87022900763359</v>
+        <v>95.95419847328245</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4053,19 +4053,19 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>KITK0105</t>
+          <t>KITK0204</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>KIT DE PERFUMES PARA CABELLO KABA</t>
+          <t>KIT PIEL LUMINOSA KABA</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="D132" t="n">
-        <v>20.72519083969465</v>
+        <v>53.81679389312977</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4081,19 +4081,19 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>KITK0204</t>
+          <t>KITK0207</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>KIT PIEL LUMINOSA KABA</t>
+          <t>KIT RUTINA FACIAL KABA</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="D133" t="n">
-        <v>53.81679389312977</v>
+        <v>4.122137404580153</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4109,19 +4109,19 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>KITK0207</t>
+          <t>KITR0101</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>KIT RUTINA FACIAL KABA</t>
+          <t>KIT ADIOS GRASA LA RECETA</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D134" t="n">
-        <v>4.122137404580153</v>
+        <v>21.87022900763359</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4321,21 +4321,21 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>KITN0103</t>
+          <t>ET0210SE</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>KIT FULL CARE</t>
+          <t>STICKER PR VIVIANA GRANDONA</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>PRODUCTO MANUFACTURADO</t>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -4347,21 +4347,23 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ET0210SE</t>
+          <t>K010103</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>STICKER PR VIVIANA GRANDONA</t>
+          <t>SHAMPOO REVITALIZANTE KABA</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>46</v>
-      </c>
-      <c r="D143" t="inlineStr"/>
+        <v>163</v>
+      </c>
+      <c r="D143" t="n">
+        <v>1231.832061068702</v>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+          <t>PRODUCTO MANUFACTURADO</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -4373,20 +4375,18 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>K010103</t>
+          <t>KITN0103</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>SHAMPOO REVITALIZANTE KABA</t>
+          <t>KIT FULL CARE</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>163</v>
-      </c>
-      <c r="D144" t="n">
-        <v>1231.832061068702</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
           <t>PRODUCTO MANUFACTURADO</t>
@@ -4481,16 +4481,16 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>K051505</t>
+          <t>K051501</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>COSMETIQUERA FACIAL GRANDE KABA</t>
+          <t>COSMETIQUERA GRANDE KABA</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
@@ -4507,16 +4507,16 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>K051501</t>
+          <t>D051501</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>COSMETIQUERA GRANDE KABA</t>
+          <t>COSMETIQUERA GRANDE DLUCHI</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>192</v>
+        <v>1</v>
       </c>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
@@ -4533,16 +4533,16 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>D051501</t>
+          <t>K051505</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>COSMETIQUERA GRANDE DLUCHI</t>
+          <t>COSMETIQUERA FACIAL GRANDE KABA</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
@@ -4611,16 +4611,16 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>K051502</t>
+          <t>O051501</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>COSMETIQUERA PEQUEÑA KABA</t>
+          <t>COSMETIQUERA PEQUEÑA OMG</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>44</v>
+        <v>330</v>
       </c>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
@@ -4637,16 +4637,16 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>O051501</t>
+          <t>K051502</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>COSMETIQUERA PEQUEÑA OMG</t>
+          <t>COSMETIQUERA PEQUEÑA KABA</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>330</v>
+        <v>44</v>
       </c>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
@@ -4689,16 +4689,16 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>K051506</t>
+          <t>K051402</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>COSMETIQUERA FACIAL PEQUEÑA KABA</t>
+          <t>CAJA DESPACHO GRANDE</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>334</v>
+        <v>45</v>
       </c>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
@@ -4715,16 +4715,16 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>K051402</t>
+          <t>K051506</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>CAJA DESPACHO GRANDE</t>
+          <t>COSMETIQUERA FACIAL PEQUEÑA KABA</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>45</v>
+        <v>334</v>
       </c>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
@@ -4903,16 +4903,16 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>KITE0101</t>
+          <t>KITD0910</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>KIT RESCATE CAPILAR + CRTO INTENSIVO</t>
+          <t>KIT PIEL CANELA MEDIO</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
@@ -4929,16 +4929,16 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>KITD0910</t>
+          <t>KITE0101</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>KIT PIEL CANELA MEDIO</t>
+          <t>KIT RESCATE CAPILAR + CRTO INTENSIVO</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
@@ -6877,21 +6877,21 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>340302</t>
+          <t>ME0546</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>340302</t>
+          <t>TUBO COLAP FOTOPROTECTOR 60ML V1</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>44000</v>
+        <v>10778</v>
       </c>
       <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr">
         <is>
-          <t>MATERIA PRIMA</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -6903,21 +6903,21 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>ME0546</t>
+          <t>340302</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>TUBO COLAP FOTOPROTECTOR 60ML V1</t>
+          <t>340302</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>10778</v>
+        <v>44000</v>
       </c>
       <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIA PRIMA</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -7215,19 +7215,19 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>KM041304</t>
+          <t>K020506</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>DROPS PINK GOLD</t>
+          <t>MASCARILLA FACIAL DE CHOCOLATE KABA</t>
         </is>
       </c>
       <c r="C252" t="n">
-        <v>5467</v>
+        <v>426</v>
       </c>
       <c r="D252" t="n">
-        <v>178.6259541984733</v>
+        <v>138.7786259541985</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
@@ -7243,19 +7243,19 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>K020506</t>
+          <t>KM041304</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>MASCARILLA FACIAL DE CHOCOLATE KABA</t>
+          <t>DROPS PINK GOLD</t>
         </is>
       </c>
       <c r="C253" t="n">
-        <v>426</v>
+        <v>5467</v>
       </c>
       <c r="D253" t="n">
-        <v>138.7786259541985</v>
+        <v>178.6259541984733</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
@@ -7271,19 +7271,19 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>K020701</t>
+          <t>KM041302</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>SOS PARCHES DE RESCATE KABA</t>
+          <t>DROPS CHAMPAGNE SILVER</t>
         </is>
       </c>
       <c r="C254" t="n">
-        <v>31</v>
+        <v>6333</v>
       </c>
       <c r="D254" t="n">
-        <v>99091.60305343512</v>
+        <v>192.7099236641222</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
@@ -7299,19 +7299,19 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>KM041302</t>
+          <t>KM041301</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>DROPS CHAMPAGNE SILVER</t>
+          <t>DROPS CHAMPAGNE GOLD</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>6333</v>
+        <v>4427</v>
       </c>
       <c r="D255" t="n">
-        <v>192.7099236641222</v>
+        <v>760.8778625954199</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
@@ -7327,19 +7327,19 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>KM041301</t>
+          <t>K020701</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>DROPS CHAMPAGNE GOLD</t>
+          <t>SOS PARCHES DE RESCATE KABA</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>4427</v>
+        <v>31</v>
       </c>
       <c r="D256" t="n">
-        <v>760.8778625954199</v>
+        <v>99091.60305343512</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
@@ -7541,19 +7541,19 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>K020604</t>
+          <t>KM041106</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>SERUM VITAMINA C KABA</t>
+          <t>CORRECTOR DE OJERAS MIEL</t>
         </is>
       </c>
       <c r="C264" t="n">
-        <v>2400</v>
+        <v>1654</v>
       </c>
       <c r="D264" t="n">
-        <v>1436.221374045801</v>
+        <v>1522.786259541985</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
@@ -7569,18 +7569,20 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>K010304USA</t>
+          <t>KM041308</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>HAIR TONIC KABA</t>
+          <t>ILUMINADOR LIQUIDO PRETTY GIRL</t>
         </is>
       </c>
       <c r="C265" t="n">
-        <v>4973</v>
-      </c>
-      <c r="D265" t="inlineStr"/>
+        <v>9802</v>
+      </c>
+      <c r="D265" t="n">
+        <v>148.3969465648855</v>
+      </c>
       <c r="E265" t="inlineStr">
         <is>
           <t>PRODUCTO MANUFACTURADO</t>
@@ -7595,19 +7597,19 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>KM041106</t>
+          <t>K020604</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>CORRECTOR DE OJERAS MIEL</t>
+          <t>SERUM VITAMINA C KABA</t>
         </is>
       </c>
       <c r="C266" t="n">
-        <v>1654</v>
+        <v>2400</v>
       </c>
       <c r="D266" t="n">
-        <v>1522.786259541985</v>
+        <v>1436.221374045801</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
@@ -7623,20 +7625,18 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>KM041308</t>
+          <t>K010304USA</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>ILUMINADOR LIQUIDO PRETTY GIRL</t>
+          <t>HAIR TONIC KABA</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>9802</v>
-      </c>
-      <c r="D267" t="n">
-        <v>148.3969465648855</v>
-      </c>
+        <v>4973</v>
+      </c>
+      <c r="D267" t="inlineStr"/>
       <c r="E267" t="inlineStr">
         <is>
           <t>PRODUCTO MANUFACTURADO</t>
@@ -7783,21 +7783,23 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>250307</t>
+          <t>K010307</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>250307</t>
+          <t>KERATINA ALISADOR PROGRESIVA KABA 250 ML</t>
         </is>
       </c>
       <c r="C273" t="n">
-        <v>16000</v>
-      </c>
-      <c r="D273" t="inlineStr"/>
+        <v>1845</v>
+      </c>
+      <c r="D273" t="n">
+        <v>2367.480916030534</v>
+      </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>MATERIA PRIMA</t>
+          <t>PRODUCTO MANUFACTURADO</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -7809,23 +7811,21 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>K010307</t>
+          <t>250307</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>KERATINA ALISADOR PROGRESIVA KABA 250 ML</t>
+          <t>250307</t>
         </is>
       </c>
       <c r="C274" t="n">
-        <v>1845</v>
-      </c>
-      <c r="D274" t="n">
-        <v>2367.480916030534</v>
-      </c>
+        <v>16000</v>
+      </c>
+      <c r="D274" t="inlineStr"/>
       <c r="E274" t="inlineStr">
         <is>
-          <t>PRODUCTO MANUFACTURADO</t>
+          <t>MATERIA PRIMA</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -8441,19 +8441,19 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>K010201</t>
+          <t>SACD031007</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>ACONDICIONADOR DE CERAMIDAS KABA</t>
+          <t>SACHET DE CREMA AUTOBRONCEADORA DLUCHI</t>
         </is>
       </c>
       <c r="C298" t="n">
-        <v>15767</v>
+        <v>22500</v>
       </c>
       <c r="D298" t="n">
-        <v>39274.69465648855</v>
+        <v>942.2519083969466</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
@@ -8469,19 +8469,19 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>SACD031007</t>
+          <t>K010201</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>SACHET DE CREMA AUTOBRONCEADORA DLUCHI</t>
+          <t>ACONDICIONADOR DE CERAMIDAS KABA</t>
         </is>
       </c>
       <c r="C299" t="n">
-        <v>22500</v>
+        <v>15767</v>
       </c>
       <c r="D299" t="n">
-        <v>942.2519083969466</v>
+        <v>39274.69465648855</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
@@ -8603,21 +8603,21 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>180103</t>
+          <t>ETC0112</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>SILICONA 1202</t>
+          <t>CAJA GLOSS GOLDEN HOUR</t>
         </is>
       </c>
       <c r="C304" t="n">
-        <v>1520000</v>
+        <v>35536</v>
       </c>
       <c r="D304" t="inlineStr"/>
       <c r="E304" t="inlineStr">
         <is>
-          <t>MATERIA PRIMA</t>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
@@ -8629,21 +8629,21 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>ETC0112</t>
+          <t>180103</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>CAJA GLOSS GOLDEN HOUR</t>
+          <t>SILICONA 1202</t>
         </is>
       </c>
       <c r="C305" t="n">
-        <v>35536</v>
+        <v>1520000</v>
       </c>
       <c r="D305" t="inlineStr"/>
       <c r="E305" t="inlineStr">
         <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+          <t>MATERIA PRIMA</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
@@ -8737,19 +8737,19 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>KM041314</t>
+          <t>KM041312</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>RUBOR LIQUIDO MARGARITA</t>
+          <t>RUBOR LIQUIDO SUNRISE</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>2354</v>
+        <v>2008</v>
       </c>
       <c r="D309" t="n">
-        <v>106.8320610687023</v>
+        <v>98.587786259542</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
@@ -8765,16 +8765,16 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>KM041311</t>
+          <t>KM041315</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>RUBOR LIQUIDO MARTINI</t>
+          <t>RUBOR LIQUIDO COCO LOCO</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>2302</v>
+        <v>2471</v>
       </c>
       <c r="D310" t="inlineStr"/>
       <c r="E310" t="inlineStr">
@@ -8791,19 +8791,19 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>KM041312</t>
+          <t>KM041313</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>RUBOR LIQUIDO SUNRISE</t>
+          <t>RUBOR LIQUIDO MANHATTAN</t>
         </is>
       </c>
       <c r="C311" t="n">
-        <v>2008</v>
+        <v>2236</v>
       </c>
       <c r="D311" t="n">
-        <v>98.587786259542</v>
+        <v>102.0229007633588</v>
       </c>
       <c r="E311" t="inlineStr">
         <is>
@@ -8819,16 +8819,16 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>KM041315</t>
+          <t>KM041311</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>RUBOR LIQUIDO COCO LOCO</t>
+          <t>RUBOR LIQUIDO MARTINI</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>2471</v>
+        <v>2302</v>
       </c>
       <c r="D312" t="inlineStr"/>
       <c r="E312" t="inlineStr">
@@ -8845,19 +8845,19 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>KM041313</t>
+          <t>KM041314</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>RUBOR LIQUIDO MANHATTAN</t>
+          <t>RUBOR LIQUIDO MARGARITA</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>2236</v>
+        <v>2354</v>
       </c>
       <c r="D313" t="n">
-        <v>102.0229007633588</v>
+        <v>106.8320610687023</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
@@ -9625,18 +9625,20 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>KM041322</t>
+          <t>O030601</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>BASE LIQUIDA MOCCA</t>
+          <t>MANTEQUILLA HIDRATANTE OMG</t>
         </is>
       </c>
       <c r="C342" t="n">
-        <v>1354</v>
-      </c>
-      <c r="D342" t="inlineStr"/>
+        <v>1939</v>
+      </c>
+      <c r="D342" t="n">
+        <v>4896.755725190839</v>
+      </c>
       <c r="E342" t="inlineStr">
         <is>
           <t>PRODUCTO MANUFACTURADO</t>
@@ -9651,19 +9653,19 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>O030601</t>
+          <t>D031003</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>MANTEQUILLA HIDRATANTE OMG</t>
+          <t>BRONCEADOR DE ZANAHORIA Y CANELA DLUCHI</t>
         </is>
       </c>
       <c r="C343" t="n">
-        <v>1939</v>
+        <v>44</v>
       </c>
       <c r="D343" t="n">
-        <v>4896.755725190839</v>
+        <v>12816.41221374046</v>
       </c>
       <c r="E343" t="inlineStr">
         <is>
@@ -9679,20 +9681,18 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>D031003</t>
+          <t>KM041322</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>BRONCEADOR DE ZANAHORIA Y CANELA DLUCHI</t>
+          <t>BASE LIQUIDA MOCCA</t>
         </is>
       </c>
       <c r="C344" t="n">
-        <v>44</v>
-      </c>
-      <c r="D344" t="n">
-        <v>12816.41221374046</v>
-      </c>
+        <v>1354</v>
+      </c>
+      <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr">
         <is>
           <t>PRODUCTO MANUFACTURADO</t>
@@ -10031,18 +10031,20 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>KM041321</t>
+          <t>KITKR0106</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>BASE LIQUIDA MIEL</t>
+          <t>KIT CRTO Y REPARACIÓN KABA +ACEITEPUNTAS</t>
         </is>
       </c>
       <c r="C357" t="n">
-        <v>1275</v>
-      </c>
-      <c r="D357" t="inlineStr"/>
+        <v>32</v>
+      </c>
+      <c r="D357" t="n">
+        <v>230.7251908396946</v>
+      </c>
       <c r="E357" t="inlineStr">
         <is>
           <t>PRODUCTO MANUFACTURADO</t>
@@ -10057,20 +10059,18 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>KITKR0106</t>
+          <t>KM041321</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>KIT CRTO Y REPARACIÓN KABA +ACEITEPUNTAS</t>
+          <t>BASE LIQUIDA MIEL</t>
         </is>
       </c>
       <c r="C358" t="n">
-        <v>32</v>
-      </c>
-      <c r="D358" t="n">
-        <v>230.7251908396946</v>
-      </c>
+        <v>1275</v>
+      </c>
+      <c r="D358" t="inlineStr"/>
       <c r="E358" t="inlineStr">
         <is>
           <t>PRODUCTO MANUFACTURADO</t>
@@ -10167,19 +10167,19 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>CAJAEMPRENDEDORA</t>
+          <t>D031007</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>CAJA EMPRENDEDORA</t>
+          <t>CREMA AUTOBRONCEADORA DLUCHI</t>
         </is>
       </c>
       <c r="C362" t="n">
-        <v>8</v>
+        <v>1183</v>
       </c>
       <c r="D362" t="n">
-        <v>15.11450381679389</v>
+        <v>4299.732824427481</v>
       </c>
       <c r="E362" t="inlineStr">
         <is>
@@ -10195,19 +10195,19 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>D031007</t>
+          <t>CAJAEMPRENDEDORA</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>CREMA AUTOBRONCEADORA DLUCHI</t>
+          <t>CAJA EMPRENDEDORA</t>
         </is>
       </c>
       <c r="C363" t="n">
-        <v>1183</v>
+        <v>8</v>
       </c>
       <c r="D363" t="n">
-        <v>4299.732824427481</v>
+        <v>15.11450381679389</v>
       </c>
       <c r="E363" t="inlineStr">
         <is>
@@ -10419,23 +10419,21 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>K030901</t>
+          <t>ETC0110</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>CREMA CORPORAL ACLARANTE KABA</t>
+          <t>CAJA EXFOLIANTE PARA LABIOS</t>
         </is>
       </c>
       <c r="C371" t="n">
-        <v>2703</v>
-      </c>
-      <c r="D371" t="n">
-        <v>11863.1679389313</v>
-      </c>
+        <v>31513</v>
+      </c>
+      <c r="D371" t="inlineStr"/>
       <c r="E371" t="inlineStr">
         <is>
-          <t>PRODUCTO MANUFACTURADO</t>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
@@ -10447,19 +10445,19 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>K020702</t>
+          <t>K010405</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>LOCION ASTRINGENTE KABA</t>
+          <t>PERFUME PARA EL CABELLO EXITOSA KABA</t>
         </is>
       </c>
       <c r="C372" t="n">
-        <v>6235</v>
+        <v>84</v>
       </c>
       <c r="D372" t="n">
-        <v>8045.038167938931</v>
+        <v>1701.068702290076</v>
       </c>
       <c r="E372" t="inlineStr">
         <is>
@@ -10475,21 +10473,23 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>ETC0110</t>
+          <t>K030901</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>CAJA EXFOLIANTE PARA LABIOS</t>
+          <t>CREMA CORPORAL ACLARANTE KABA</t>
         </is>
       </c>
       <c r="C373" t="n">
-        <v>31513</v>
-      </c>
-      <c r="D373" t="inlineStr"/>
+        <v>2703</v>
+      </c>
+      <c r="D373" t="n">
+        <v>11863.1679389313</v>
+      </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+          <t>PRODUCTO MANUFACTURADO</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
@@ -10501,19 +10501,19 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>K010405</t>
+          <t>K020702</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>PERFUME PARA EL CABELLO EXITOSA KABA</t>
+          <t>LOCION ASTRINGENTE KABA</t>
         </is>
       </c>
       <c r="C374" t="n">
-        <v>84</v>
+        <v>6235</v>
       </c>
       <c r="D374" t="n">
-        <v>1701.068702290076</v>
+        <v>8045.038167938931</v>
       </c>
       <c r="E374" t="inlineStr">
         <is>
@@ -10581,19 +10581,19 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>K010305</t>
+          <t>D030603</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>TRATAMIENTO REPARACION SOS KABA</t>
+          <t>MANTEQUILLA CORPORAL DLUCHI</t>
         </is>
       </c>
       <c r="C377" t="n">
-        <v>3164</v>
+        <v>3283</v>
       </c>
       <c r="D377" t="n">
-        <v>1825.763358778626</v>
+        <v>6729.73282442748</v>
       </c>
       <c r="E377" t="inlineStr">
         <is>
@@ -10609,19 +10609,19 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>D030603</t>
+          <t>K010305</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>MANTEQUILLA CORPORAL DLUCHI</t>
+          <t>TRATAMIENTO REPARACION SOS KABA</t>
         </is>
       </c>
       <c r="C378" t="n">
-        <v>3283</v>
+        <v>3164</v>
       </c>
       <c r="D378" t="n">
-        <v>6729.73282442748</v>
+        <v>1825.763358778626</v>
       </c>
       <c r="E378" t="inlineStr">
         <is>
@@ -11105,20 +11105,18 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>K010104</t>
+          <t>DREAMBAG</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>SHAMPOO REPARACION SOS KABA</t>
+          <t>KIT BOLSA SORPRESA</t>
         </is>
       </c>
       <c r="C396" t="n">
-        <v>4471</v>
-      </c>
-      <c r="D396" t="n">
-        <v>834.0458015267176</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="D396" t="inlineStr"/>
       <c r="E396" t="inlineStr">
         <is>
           <t>PRODUCTO MANUFACTURADO</t>
@@ -11133,18 +11131,20 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>DREAMBAG</t>
+          <t>K010104</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>KIT BOLSA SORPRESA</t>
+          <t>SHAMPOO REPARACION SOS KABA</t>
         </is>
       </c>
       <c r="C397" t="n">
-        <v>179</v>
-      </c>
-      <c r="D397" t="inlineStr"/>
+        <v>4471</v>
+      </c>
+      <c r="D397" t="n">
+        <v>834.0458015267176</v>
+      </c>
       <c r="E397" t="inlineStr">
         <is>
           <t>PRODUCTO MANUFACTURADO</t>
@@ -11159,19 +11159,19 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>KM041202</t>
+          <t>KM041105</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>LIP GLOSS GOLDEN HOUR</t>
+          <t>CORRECTOR DE OJERAS MACADAMIA</t>
         </is>
       </c>
       <c r="C398" t="n">
-        <v>432</v>
+        <v>216</v>
       </c>
       <c r="D398" t="n">
-        <v>171.412213740458</v>
+        <v>347.2900763358779</v>
       </c>
       <c r="E398" t="inlineStr">
         <is>
@@ -11187,19 +11187,19 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>KM041105</t>
+          <t>KM041202</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>CORRECTOR DE OJERAS MACADAMIA</t>
+          <t>LIP GLOSS GOLDEN HOUR</t>
         </is>
       </c>
       <c r="C399" t="n">
-        <v>216</v>
+        <v>432</v>
       </c>
       <c r="D399" t="n">
-        <v>347.2900763358779</v>
+        <v>171.412213740458</v>
       </c>
       <c r="E399" t="inlineStr">
         <is>
@@ -11351,19 +11351,19 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>KITR0104</t>
+          <t>KITK0207</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>KIT DUO ANTIGRASA LA RECETA</t>
+          <t>KIT RUTINA FACIAL KABA</t>
         </is>
       </c>
       <c r="C405" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D405" t="n">
-        <v>24.96183206106871</v>
+        <v>4.122137404580153</v>
       </c>
       <c r="E405" t="inlineStr">
         <is>
@@ -11379,19 +11379,19 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>KITK0207</t>
+          <t>KITR0104</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>KIT RUTINA FACIAL KABA</t>
+          <t>KIT DUO ANTIGRASA LA RECETA</t>
         </is>
       </c>
       <c r="C406" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D406" t="n">
-        <v>4.122137404580153</v>
+        <v>24.96183206106871</v>
       </c>
       <c r="E406" t="inlineStr">
         <is>
@@ -11407,18 +11407,20 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>K010206USA</t>
+          <t>KM041108</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>HAIR CONDITIONER WITH CERAMIDES 1 LITRO</t>
+          <t>GEL FIJADOR DE CEJAS</t>
         </is>
       </c>
       <c r="C407" t="n">
-        <v>907</v>
-      </c>
-      <c r="D407" t="inlineStr"/>
+        <v>1512</v>
+      </c>
+      <c r="D407" t="n">
+        <v>4274.312977099236</v>
+      </c>
       <c r="E407" t="inlineStr">
         <is>
           <t>PRODUCTO MANUFACTURADO</t>
@@ -11433,19 +11435,19 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>KM041108</t>
+          <t>KM041303</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>GEL FIJADOR DE CEJAS</t>
+          <t>DROPS HONEY GOLD</t>
         </is>
       </c>
       <c r="C408" t="n">
-        <v>1512</v>
+        <v>5060</v>
       </c>
       <c r="D408" t="n">
-        <v>4274.312977099236</v>
+        <v>531.7557251908397</v>
       </c>
       <c r="E408" t="inlineStr">
         <is>
@@ -11461,20 +11463,18 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>KM041303</t>
+          <t>K010206USA</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>DROPS HONEY GOLD</t>
+          <t>HAIR CONDITIONER WITH CERAMIDES 1 LITRO</t>
         </is>
       </c>
       <c r="C409" t="n">
-        <v>5060</v>
-      </c>
-      <c r="D409" t="n">
-        <v>531.7557251908397</v>
-      </c>
+        <v>907</v>
+      </c>
+      <c r="D409" t="inlineStr"/>
       <c r="E409" t="inlineStr">
         <is>
           <t>PRODUCTO MANUFACTURADO</t>
@@ -12087,21 +12087,21 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>155301</t>
+          <t>ME1011</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>ESTOGEL M</t>
+          <t>LOTIÓN PUMP 28/410 SILVER/WHITE</t>
         </is>
       </c>
       <c r="C433" t="n">
-        <v>100000</v>
+        <v>326790</v>
       </c>
       <c r="D433" t="inlineStr"/>
       <c r="E433" t="inlineStr">
         <is>
-          <t>MATERIA PRIMA</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F433" t="inlineStr">
@@ -12113,21 +12113,21 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>ME1011</t>
+          <t>155301</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>LOTIÓN PUMP 28/410 SILVER/WHITE</t>
+          <t>ESTOGEL M</t>
         </is>
       </c>
       <c r="C434" t="n">
-        <v>326790</v>
+        <v>100000</v>
       </c>
       <c r="D434" t="inlineStr"/>
       <c r="E434" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIA PRIMA</t>
         </is>
       </c>
       <c r="F434" t="inlineStr">
@@ -13795,21 +13795,21 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>ME0526</t>
+          <t>K051407</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>ENVASE VIDRIO ROSADO EXITOSA 120ML</t>
+          <t>BOLSA KABA CARTUCHERA</t>
         </is>
       </c>
       <c r="C499" t="n">
-        <v>17952</v>
+        <v>20234</v>
       </c>
       <c r="D499" t="inlineStr"/>
       <c r="E499" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
         </is>
       </c>
       <c r="F499" t="inlineStr">
@@ -13821,16 +13821,16 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>K051407</t>
+          <t>R051401</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>BOLSA KABA CARTUCHERA</t>
+          <t>BOLSA LA RECETA CARTUCHERA</t>
         </is>
       </c>
       <c r="C500" t="n">
-        <v>20234</v>
+        <v>18193</v>
       </c>
       <c r="D500" t="inlineStr"/>
       <c r="E500" t="inlineStr">
@@ -13847,21 +13847,21 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>R051401</t>
+          <t>ME0526</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>BOLSA LA RECETA CARTUCHERA</t>
+          <t>ENVASE VIDRIO ROSADO EXITOSA 120ML</t>
         </is>
       </c>
       <c r="C501" t="n">
-        <v>18193</v>
+        <v>17952</v>
       </c>
       <c r="D501" t="inlineStr"/>
       <c r="E501" t="inlineStr">
         <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F501" t="inlineStr">
@@ -14595,21 +14595,21 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>K051501</t>
+          <t>DISACK010302</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>COSMETIQUERA GRANDE KABA</t>
+          <t>DISPLEY SACHET DE BIO MASCARILLA CAPILAR</t>
         </is>
       </c>
       <c r="C531" t="n">
-        <v>3063</v>
+        <v>2</v>
       </c>
       <c r="D531" t="inlineStr"/>
       <c r="E531" t="inlineStr">
         <is>
-          <t>COMPRA GRAVADA SIN LOTES</t>
+          <t>PRODUCTO MANUFACTURADO</t>
         </is>
       </c>
       <c r="F531" t="inlineStr">
@@ -14621,18 +14621,20 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>DISACK010302</t>
+          <t>K010202</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>DISPLEY SACHET DE BIO MASCARILLA CAPILAR</t>
+          <t>ACONDICIONADOR KIDS KABA</t>
         </is>
       </c>
       <c r="C532" t="n">
-        <v>2</v>
-      </c>
-      <c r="D532" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="D532" t="n">
+        <v>1538.24427480916</v>
+      </c>
       <c r="E532" t="inlineStr">
         <is>
           <t>PRODUCTO MANUFACTURADO</t>
@@ -14647,20 +14649,18 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>K010202</t>
+          <t>DISACK010101</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>ACONDICIONADOR KIDS KABA</t>
+          <t>DISPLEY SACHET DE SHAMPOO DE CEBOLLA KAB</t>
         </is>
       </c>
       <c r="C533" t="n">
-        <v>100</v>
-      </c>
-      <c r="D533" t="n">
-        <v>1538.24427480916</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D533" t="inlineStr"/>
       <c r="E533" t="inlineStr">
         <is>
           <t>PRODUCTO MANUFACTURADO</t>
@@ -14675,21 +14675,21 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>KITN0103</t>
+          <t>K051501</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>KIT FULL CARE</t>
+          <t>COSMETIQUERA GRANDE KABA</t>
         </is>
       </c>
       <c r="C534" t="n">
-        <v>7</v>
+        <v>3063</v>
       </c>
       <c r="D534" t="inlineStr"/>
       <c r="E534" t="inlineStr">
         <is>
-          <t>PRODUCTO MANUFACTURADO</t>
+          <t>COMPRA GRAVADA SIN LOTES</t>
         </is>
       </c>
       <c r="F534" t="inlineStr">
@@ -14701,16 +14701,16 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>DISACK010101</t>
+          <t>KITN0103</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>DISPLEY SACHET DE SHAMPOO DE CEBOLLA KAB</t>
+          <t>KIT FULL CARE</t>
         </is>
       </c>
       <c r="C535" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D535" t="inlineStr"/>
       <c r="E535" t="inlineStr">
@@ -14807,16 +14807,16 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>K051505</t>
+          <t>D051501</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>COSMETIQUERA FACIAL GRANDE KABA</t>
+          <t>COSMETIQUERA GRANDE DLUCHI</t>
         </is>
       </c>
       <c r="C539" t="n">
-        <v>26550</v>
+        <v>30008</v>
       </c>
       <c r="D539" t="inlineStr"/>
       <c r="E539" t="inlineStr">
@@ -14833,16 +14833,16 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>D051501</t>
+          <t>K051505</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>COSMETIQUERA GRANDE DLUCHI</t>
+          <t>COSMETIQUERA FACIAL GRANDE KABA</t>
         </is>
       </c>
       <c r="C540" t="n">
-        <v>30008</v>
+        <v>26550</v>
       </c>
       <c r="D540" t="inlineStr"/>
       <c r="E540" t="inlineStr">
@@ -14911,16 +14911,16 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>K051502</t>
+          <t>O051501</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>COSMETIQUERA PEQUEÑA KABA</t>
+          <t>COSMETIQUERA PEQUEÑA OMG</t>
         </is>
       </c>
       <c r="C543" t="n">
-        <v>12000</v>
+        <v>14400</v>
       </c>
       <c r="D543" t="inlineStr"/>
       <c r="E543" t="inlineStr">
@@ -14937,16 +14937,16 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>O051501</t>
+          <t>K051502</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>COSMETIQUERA PEQUEÑA OMG</t>
+          <t>COSMETIQUERA PEQUEÑA KABA</t>
         </is>
       </c>
       <c r="C544" t="n">
-        <v>14400</v>
+        <v>12000</v>
       </c>
       <c r="D544" t="inlineStr"/>
       <c r="E544" t="inlineStr">
@@ -14989,16 +14989,16 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>K051506</t>
+          <t>K051402</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>COSMETIQUERA FACIAL PEQUEÑA KABA</t>
+          <t>CAJA DESPACHO GRANDE</t>
         </is>
       </c>
       <c r="C546" t="n">
-        <v>16800</v>
+        <v>27500</v>
       </c>
       <c r="D546" t="inlineStr"/>
       <c r="E546" t="inlineStr">
@@ -15015,16 +15015,16 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>K051402</t>
+          <t>K051506</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>CAJA DESPACHO GRANDE</t>
+          <t>COSMETIQUERA FACIAL PEQUEÑA KABA</t>
         </is>
       </c>
       <c r="C547" t="n">
-        <v>27500</v>
+        <v>16800</v>
       </c>
       <c r="D547" t="inlineStr"/>
       <c r="E547" t="inlineStr">
@@ -16439,12 +16439,12 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>VB020303-01-03-L-24</t>
+          <t>VB020105-01-02-M-13</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-L-HOJAS NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-M-NARANJA</t>
         </is>
       </c>
       <c r="C604" t="n">
@@ -16461,16 +16461,16 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>VB020105-01-01-S-08</t>
+          <t>VB020303-01-03-L-24</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-S-AZUL REY</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-L-HOJAS NEGRO</t>
         </is>
       </c>
       <c r="C605" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D605" t="inlineStr"/>
       <c r="E605" t="inlineStr"/>
@@ -16483,16 +16483,16 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>VB020103-03-02-M-32</t>
+          <t>VB020105-01-01-S-08</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-M-SELVA PAJAROS</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-S-AZUL REY</t>
         </is>
       </c>
       <c r="C606" t="n">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="D606" t="inlineStr"/>
       <c r="E606" t="inlineStr"/>
@@ -16505,16 +16505,16 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>VB020303-01-03-L-25</t>
+          <t>VB020103-03-02-M-32</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-L-HOJAS VERDES</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-M-SELVA PAJAROS</t>
         </is>
       </c>
       <c r="C607" t="n">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="D607" t="inlineStr"/>
       <c r="E607" t="inlineStr"/>
@@ -16527,16 +16527,16 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>VB020105-01-02-M-13</t>
+          <t>VB020303-01-03-L-25</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-M-NARANJA</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-L-HOJAS VERDES</t>
         </is>
       </c>
       <c r="C608" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D608" t="inlineStr"/>
       <c r="E608" t="inlineStr"/>
@@ -16549,16 +16549,16 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>VB020303-01-03-L-30</t>
+          <t>VB020103-03-01-S-32</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-L-PLUMAS</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-S-SELVA PAJAROS</t>
         </is>
       </c>
       <c r="C609" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="D609" t="inlineStr"/>
       <c r="E609" t="inlineStr"/>
@@ -16571,16 +16571,16 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>VB020103-03-01-S-32</t>
+          <t>VB020303-01-03-L-30</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-S-SELVA PAJAROS</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-L-PLUMAS</t>
         </is>
       </c>
       <c r="C610" t="n">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="D610" t="inlineStr"/>
       <c r="E610" t="inlineStr"/>
@@ -16593,12 +16593,12 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>VB020103-01-01-S-26</t>
+          <t>VB020103-01-03-L-26</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI-S-MISTICO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI-L-MISTICO</t>
         </is>
       </c>
       <c r="C611" t="n">
@@ -16615,16 +16615,16 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>VB020105-01-03-L-05</t>
+          <t>VB020105-01-01-S-11</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-L-AMARILLO NEON</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-S-FUCSIA NEON</t>
         </is>
       </c>
       <c r="C612" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D612" t="inlineStr"/>
       <c r="E612" t="inlineStr"/>
@@ -16637,16 +16637,16 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>VB020204-01-03-L-05</t>
+          <t>VB020103-01-01-S-26</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-L-AMARILLO NEON</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI-S-MISTICO</t>
         </is>
       </c>
       <c r="C613" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D613" t="inlineStr"/>
       <c r="E613" t="inlineStr"/>
@@ -16659,16 +16659,16 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>VB020303-01-02-M-30</t>
+          <t>VB020105-01-03-L-05</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-M-PLUMAS</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-L-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C614" t="n">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="D614" t="inlineStr"/>
       <c r="E614" t="inlineStr"/>
@@ -16681,16 +16681,16 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>VB020303-01-01-S-30</t>
+          <t>VB020204-01-03-L-05</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-S-PLUMAS</t>
+          <t>VB DOS PIEZAS TOP PANTY-L-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C615" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D615" t="inlineStr"/>
       <c r="E615" t="inlineStr"/>
@@ -16703,16 +16703,16 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>VB020103-03-01-S-20</t>
+          <t>VB020303-01-02-M-30</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-S-ANIMAL PRINT FLORES</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-M-PLUMAS</t>
         </is>
       </c>
       <c r="C616" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D616" t="inlineStr"/>
       <c r="E616" t="inlineStr"/>
@@ -16725,16 +16725,16 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>VB020105-01-02-M-08</t>
+          <t>VB020303-01-01-S-30</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-M-AZUL REY</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-S-PLUMAS</t>
         </is>
       </c>
       <c r="C617" t="n">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="D617" t="inlineStr"/>
       <c r="E617" t="inlineStr"/>
@@ -16747,16 +16747,16 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>VB020103-01-03-L-26</t>
+          <t>VB020103-03-01-S-20</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI-L-MISTICO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-S-ANIMAL PRINT FLORES</t>
         </is>
       </c>
       <c r="C618" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D618" t="inlineStr"/>
       <c r="E618" t="inlineStr"/>
@@ -16769,12 +16769,12 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>VB020105-01-01-S-11</t>
+          <t>VB020105-01-03-L-15</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-S-FUCSIA NEON</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-L-PURPURA</t>
         </is>
       </c>
       <c r="C619" t="n">
@@ -16791,16 +16791,16 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>VB020105-01-03-L-15</t>
+          <t>VB020105-01-02-M-15</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-L-PURPURA</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-M-PURPURA</t>
         </is>
       </c>
       <c r="C620" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D620" t="inlineStr"/>
       <c r="E620" t="inlineStr"/>
@@ -16813,16 +16813,16 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>VB020105-01-02-M-15</t>
+          <t>VB020105-01-02-M-08</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-M-PURPURA</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-M-AZUL REY</t>
         </is>
       </c>
       <c r="C621" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D621" t="inlineStr"/>
       <c r="E621" t="inlineStr"/>
@@ -18617,16 +18617,16 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>VB0306-01-02-M-14</t>
+          <t>VB020105-01-03-L-16</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-M-PALO DE ROSA</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-L-ROJO</t>
         </is>
       </c>
       <c r="C703" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D703" t="inlineStr"/>
       <c r="E703" t="inlineStr"/>
@@ -18639,12 +18639,12 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>VB0306-01-01-S-14</t>
+          <t>VB020105-01-02-M-16</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-S-PALO DE ROSA</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-M-ROJO</t>
         </is>
       </c>
       <c r="C704" t="n">
@@ -18661,16 +18661,16 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>VB0306-01-03-L-16</t>
+          <t>VB020105-01-01-S-16</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-L-ROJO</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-S-ROJO</t>
         </is>
       </c>
       <c r="C705" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D705" t="inlineStr"/>
       <c r="E705" t="inlineStr"/>
@@ -18683,16 +18683,16 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>VB0306-01-02-M-16</t>
+          <t>VB020204-01-03-L-15</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-M-ROJO</t>
+          <t>VB DOS PIEZAS TOP PANTY-L-PURPURA</t>
         </is>
       </c>
       <c r="C706" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D706" t="inlineStr"/>
       <c r="E706" t="inlineStr"/>
@@ -18705,16 +18705,16 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>VB0306-01-03-L-14</t>
+          <t>VB0103-01-03-L-32</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-L-PALO DE ROSA</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-L-SELVA PAJAROS</t>
         </is>
       </c>
       <c r="C707" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D707" t="inlineStr"/>
       <c r="E707" t="inlineStr"/>
@@ -18727,16 +18727,16 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>VB0306-01-01-S-16</t>
+          <t>VB020202-01-03-L-23</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-S-ROJO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-L-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C708" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D708" t="inlineStr"/>
       <c r="E708" t="inlineStr"/>
@@ -18749,12 +18749,12 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>VB0103-01-01-S-01</t>
+          <t>VB020202-01-01-S-23</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-S-BLANCO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-S-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C709" t="n">
@@ -18771,16 +18771,16 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>VB0103-01-03-L-01</t>
+          <t>VB0103-01-02-M-32</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-L-BLANCO</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-M-SELVA PAJAROS</t>
         </is>
       </c>
       <c r="C710" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D710" t="inlineStr"/>
       <c r="E710" t="inlineStr"/>
@@ -18793,16 +18793,16 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>VB0103-01-01-S-02</t>
+          <t>VB0302-01-02-M-01</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-S-NEGRO</t>
+          <t>PANTALON ALTO-M-BLANCO</t>
         </is>
       </c>
       <c r="C711" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D711" t="inlineStr"/>
       <c r="E711" t="inlineStr"/>
@@ -18815,16 +18815,16 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>VB0103-01-03-L-16</t>
+          <t>VB020204-01-03-L-08</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-L-ROJO</t>
+          <t>VB DOS PIEZAS TOP PANTY-L-AZUL REY</t>
         </is>
       </c>
       <c r="C712" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D712" t="inlineStr"/>
       <c r="E712" t="inlineStr"/>
@@ -18837,16 +18837,16 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>VB0103-01-01-S-16</t>
+          <t>VB0103-01-01-S-32</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-S-ROJO</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-S-SELVA PAJAROS</t>
         </is>
       </c>
       <c r="C713" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D713" t="inlineStr"/>
       <c r="E713" t="inlineStr"/>
@@ -18859,16 +18859,16 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>VB020104-01-01-S-02</t>
+          <t>VB020204-01-03-L-07</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-S-NEGRO</t>
+          <t>VB DOS PIEZAS TOP PANTY-L-AZUL CIAN</t>
         </is>
       </c>
       <c r="C714" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D714" t="inlineStr"/>
       <c r="E714" t="inlineStr"/>
@@ -18881,16 +18881,16 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>VB020104-01-02-M-02</t>
+          <t>VB020103-02-03-L-01</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-M-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-L-BLANCO</t>
         </is>
       </c>
       <c r="C715" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D715" t="inlineStr"/>
       <c r="E715" t="inlineStr"/>
@@ -18903,16 +18903,16 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>VB020104-01-03-L-02</t>
+          <t>VB0105-01-01-S-23</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-L-NEGRO</t>
+          <t>VB ENTERO TANGA-S-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C716" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="D716" t="inlineStr"/>
       <c r="E716" t="inlineStr"/>
@@ -18925,16 +18925,16 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>VB0103-01-02-M-16</t>
+          <t>VB020204-01-03-L-13</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-M-ROJO</t>
+          <t>VB DOS PIEZAS TOP PANTY-L-NARANJA</t>
         </is>
       </c>
       <c r="C717" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D717" t="inlineStr"/>
       <c r="E717" t="inlineStr"/>
@@ -18947,16 +18947,16 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>VB020205-03-01-S-21</t>
+          <t>VB020103-02-03-L-17</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-S-ASTRAL</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-L-ROSADO</t>
         </is>
       </c>
       <c r="C718" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D718" t="inlineStr"/>
       <c r="E718" t="inlineStr"/>
@@ -18969,16 +18969,16 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>VB020205-03-02-M-21</t>
+          <t>VB020204-01-01-S-13</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-M-ASTRAL</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-NARANJA</t>
         </is>
       </c>
       <c r="C719" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D719" t="inlineStr"/>
       <c r="E719" t="inlineStr"/>
@@ -18991,16 +18991,16 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>VB020205-03-03-L-21</t>
+          <t>VB0302-01-03-L-01</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-L-ASTRAL</t>
+          <t>PANTALON ALTO-L-BLANCO</t>
         </is>
       </c>
       <c r="C720" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D720" t="inlineStr"/>
       <c r="E720" t="inlineStr"/>
@@ -19013,16 +19013,16 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>VB020205-02-03-L-04</t>
+          <t>VB020103-02-03-L-02</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-L-AMARILLO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-L-NEGRO</t>
         </is>
       </c>
       <c r="C721" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D721" t="inlineStr"/>
       <c r="E721" t="inlineStr"/>
@@ -19035,16 +19035,16 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>VB020205-02-03-L-07</t>
+          <t>VB020204-01-02-M-07</t>
         </is>
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-L-AZUL CIAN</t>
+          <t>VB DOS PIEZAS TOP PANTY-M-AZUL CIAN</t>
         </is>
       </c>
       <c r="C722" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D722" t="inlineStr"/>
       <c r="E722" t="inlineStr"/>
@@ -19057,16 +19057,16 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>VB020205-02-03-L-22</t>
+          <t>VB020204-01-01-S-08</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-L-FLORES</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-AZUL REY</t>
         </is>
       </c>
       <c r="C723" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D723" t="inlineStr"/>
       <c r="E723" t="inlineStr"/>
@@ -19079,16 +19079,16 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>VB020205-02-03-L-10</t>
+          <t>VB0302-01-03-L-02</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-L-FUCSIA</t>
+          <t>PANTALON ALTO-L-NEGRO</t>
         </is>
       </c>
       <c r="C724" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="D724" t="inlineStr"/>
       <c r="E724" t="inlineStr"/>
@@ -19101,16 +19101,16 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>VB020205-02-03-L-12</t>
+          <t>VB020204-01-01-S-11</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-L-MORADO</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-FUCSIA NEON</t>
         </is>
       </c>
       <c r="C725" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D725" t="inlineStr"/>
       <c r="E725" t="inlineStr"/>
@@ -19123,16 +19123,16 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>VB020205-02-02-M-04</t>
+          <t>VB020103-02-01-S-17</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-M-AMARILLO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-S-ROSADO</t>
         </is>
       </c>
       <c r="C726" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D726" t="inlineStr"/>
       <c r="E726" t="inlineStr"/>
@@ -19145,16 +19145,16 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>VB020205-02-02-M-07</t>
+          <t>VB0302-01-01-S-01</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-M-AZUL CIAN</t>
+          <t>PANTALON ALTO-S-BLANCO</t>
         </is>
       </c>
       <c r="C727" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D727" t="inlineStr"/>
       <c r="E727" t="inlineStr"/>
@@ -19167,16 +19167,16 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>VB020205-02-02-M-22</t>
+          <t>VB0105-01-02-M-23</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-M-FLORES</t>
+          <t>VB ENTERO TANGA-M-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C728" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="D728" t="inlineStr"/>
       <c r="E728" t="inlineStr"/>
@@ -19189,16 +19189,16 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>VB020205-02-01-S-04</t>
+          <t>VB020103-02-02-M-17</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-S-AMARILLO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-M-ROSADO</t>
         </is>
       </c>
       <c r="C729" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D729" t="inlineStr"/>
       <c r="E729" t="inlineStr"/>
@@ -19211,16 +19211,16 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>VB020205-02-01-S-07</t>
+          <t>VB020204-01-01-S-05</t>
         </is>
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-S-AZUL CIAN</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C730" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D730" t="inlineStr"/>
       <c r="E730" t="inlineStr"/>
@@ -19233,16 +19233,16 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>VB020205-02-01-S-22</t>
+          <t>VB020303-01-01-S-26</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-S-FLORES</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-S-MISTICO</t>
         </is>
       </c>
       <c r="C731" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D731" t="inlineStr"/>
       <c r="E731" t="inlineStr"/>
@@ -19255,16 +19255,16 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>VB020205-02-01-S-10</t>
+          <t>VB020103-02-02-M-03</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-S-FUCSIA</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-M-AGUAMARINA</t>
         </is>
       </c>
       <c r="C732" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="D732" t="inlineStr"/>
       <c r="E732" t="inlineStr"/>
@@ -19277,16 +19277,16 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>VB020205-02-01-S-12</t>
+          <t>VB020103-02-01-S-02</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-S-MORADO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-S-NEGRO</t>
         </is>
       </c>
       <c r="C733" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D733" t="inlineStr"/>
       <c r="E733" t="inlineStr"/>
@@ -19299,16 +19299,16 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>VB020202-01-03-L-04</t>
+          <t>VB020103-02-01-S-03</t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-L-AMARILLO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-S-AGUAMARINA</t>
         </is>
       </c>
       <c r="C734" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D734" t="inlineStr"/>
       <c r="E734" t="inlineStr"/>
@@ -19321,16 +19321,16 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>VB020202-01-03-L-08</t>
+          <t>VB020204-01-03-L-11</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-L-AZUL REY</t>
+          <t>VB DOS PIEZAS TOP PANTY-L-FUCSIA NEON</t>
         </is>
       </c>
       <c r="C735" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D735" t="inlineStr"/>
       <c r="E735" t="inlineStr"/>
@@ -19343,16 +19343,16 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>VB020202-01-03-L-19</t>
+          <t>VB020103-02-03-L-03</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-L-ANIMAL PRINT CAFÉ</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-L-AGUAMARINA</t>
         </is>
       </c>
       <c r="C736" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D736" t="inlineStr"/>
       <c r="E736" t="inlineStr"/>
@@ -19365,16 +19365,16 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>VB020202-01-03-L-22</t>
+          <t>VB020204-01-02-M-13</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-L-FLORES</t>
+          <t>VB DOS PIEZAS TOP PANTY-M-NARANJA</t>
         </is>
       </c>
       <c r="C737" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="D737" t="inlineStr"/>
       <c r="E737" t="inlineStr"/>
@@ -19387,16 +19387,16 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>VB020202-01-02-M-04</t>
+          <t>VB020204-01-02-M-11</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-M-AMARILLO</t>
+          <t>VB DOS PIEZAS TOP PANTY-M-FUCSIA NEON</t>
         </is>
       </c>
       <c r="C738" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D738" t="inlineStr"/>
       <c r="E738" t="inlineStr"/>
@@ -19409,16 +19409,16 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>VB020202-01-02-M-08</t>
+          <t>VB020204-01-01-S-07</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-M-AZUL REY</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-AZUL CIAN</t>
         </is>
       </c>
       <c r="C739" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D739" t="inlineStr"/>
       <c r="E739" t="inlineStr"/>
@@ -19431,16 +19431,16 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>VB020202-01-02-M-19</t>
+          <t>VB020204-01-01-S-15</t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-M-ANIMAL PRINT CAFÉ</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-PURPURA</t>
         </is>
       </c>
       <c r="C740" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="D740" t="inlineStr"/>
       <c r="E740" t="inlineStr"/>
@@ -19453,16 +19453,16 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>VB020202-01-02-M-22</t>
+          <t>VB020303-01-03-L-26</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-M-FLORES</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-L-MISTICO</t>
         </is>
       </c>
       <c r="C741" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="D741" t="inlineStr"/>
       <c r="E741" t="inlineStr"/>
@@ -19475,16 +19475,16 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>VB020202-01-01-S-04</t>
+          <t>VB020303-01-02-M-26</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-S-AMARILLO</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-M-MISTICO</t>
         </is>
       </c>
       <c r="C742" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="D742" t="inlineStr"/>
       <c r="E742" t="inlineStr"/>
@@ -19497,16 +19497,16 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>VB020202-01-01-S-19</t>
+          <t>VB020204-01-02-M-08</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-S-ANIMAL PRINT CAFÉ</t>
+          <t>VB DOS PIEZAS TOP PANTY-M-AZUL REY</t>
         </is>
       </c>
       <c r="C743" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D743" t="inlineStr"/>
       <c r="E743" t="inlineStr"/>
@@ -19519,16 +19519,16 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>VB020202-01-01-S-22</t>
+          <t>VB020202-01-02-M-23</t>
         </is>
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-S-FLORES</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-M-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C744" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D744" t="inlineStr"/>
       <c r="E744" t="inlineStr"/>
@@ -19541,16 +19541,16 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>VB020202-01-01-S-08</t>
+          <t>VB0105-01-03-L-23</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-S-AZUL REY</t>
+          <t>VB ENTERO TANGA-L-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C745" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="D745" t="inlineStr"/>
       <c r="E745" t="inlineStr"/>
@@ -19563,16 +19563,16 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>VB0105-01-01-S-31</t>
+          <t>VB020203-01-03-L-01</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA-S-SAFARI</t>
+          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-L-BLANCO</t>
         </is>
       </c>
       <c r="C746" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="D746" t="inlineStr"/>
       <c r="E746" t="inlineStr"/>
@@ -19585,16 +19585,16 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>VB0105-01-03-L-31</t>
+          <t>VB020203-01-02-M-01</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA-L-SAFARI</t>
+          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-M-BLANCO</t>
         </is>
       </c>
       <c r="C747" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D747" t="inlineStr"/>
       <c r="E747" t="inlineStr"/>
@@ -19607,16 +19607,16 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>VB020402-01-01-S-31</t>
+          <t>VB0302-01-02-M-02</t>
         </is>
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS BUSO TALLE ALTO-S-SAFARI</t>
+          <t>PANTALON ALTO-M-NEGRO</t>
         </is>
       </c>
       <c r="C748" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D748" t="inlineStr"/>
       <c r="E748" t="inlineStr"/>
@@ -19629,16 +19629,16 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>VB020402-01-02-M-31</t>
+          <t>VB020204-01-02-M-05</t>
         </is>
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS BUSO TALLE ALTO-M-SAFARI</t>
+          <t>VB DOS PIEZAS TOP PANTY-M-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C749" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D749" t="inlineStr"/>
       <c r="E749" t="inlineStr"/>
@@ -19651,16 +19651,16 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>VB0105-01-02-M-31</t>
+          <t>VB020202-01-03-L-07</t>
         </is>
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA-M-SAFARI</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-L-AZUL CIAN</t>
         </is>
       </c>
       <c r="C750" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D750" t="inlineStr"/>
       <c r="E750" t="inlineStr"/>
@@ -19673,16 +19673,16 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>VB020101-01-01-S-05</t>
+          <t>VB020202-01-02-M-07</t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-AMARILLO NEON</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-M-AZUL CIAN</t>
         </is>
       </c>
       <c r="C751" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D751" t="inlineStr"/>
       <c r="E751" t="inlineStr"/>
@@ -19695,16 +19695,16 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>VB020101-01-03-L-05</t>
+          <t>VB020202-01-01-S-07</t>
         </is>
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-AMARILLO NEON</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-S-AZUL CIAN</t>
         </is>
       </c>
       <c r="C752" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D752" t="inlineStr"/>
       <c r="E752" t="inlineStr"/>
@@ -19717,16 +19717,16 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>VB020101-01-03-L-27</t>
+          <t>VB020101-01-01-S-15</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-PITON AZUL</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-PURPURA</t>
         </is>
       </c>
       <c r="C753" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D753" t="inlineStr"/>
       <c r="E753" t="inlineStr"/>
@@ -19739,16 +19739,16 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>VB020101-01-01-S-29</t>
+          <t>VB020105-01-02-M-01</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-PITON ROSADO</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-M-BLANCO</t>
         </is>
       </c>
       <c r="C754" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D754" t="inlineStr"/>
       <c r="E754" t="inlineStr"/>
@@ -19761,12 +19761,12 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>VB020101-01-02-M-29</t>
+          <t>VB020203-01-03-L-02</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-PITON ROSADO</t>
+          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-L-NEGRO</t>
         </is>
       </c>
       <c r="C755" t="n">
@@ -19783,16 +19783,16 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>VB020101-01-03-L-29</t>
+          <t>VB020202-01-03-L-02</t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-PITON ROSADO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-L-NEGRO</t>
         </is>
       </c>
       <c r="C756" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D756" t="inlineStr"/>
       <c r="E756" t="inlineStr"/>
@@ -19805,16 +19805,16 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>VB020101-01-02-M-05</t>
+          <t>VB020202-01-01-S-02</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-AMARILLO NEON</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-S-NEGRO</t>
         </is>
       </c>
       <c r="C757" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="D757" t="inlineStr"/>
       <c r="E757" t="inlineStr"/>
@@ -19827,16 +19827,16 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>VB020105-01-03-L-16</t>
+          <t>VB020202-01-03-L-09</t>
         </is>
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-L-ROJO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-L-BEIGE</t>
         </is>
       </c>
       <c r="C758" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D758" t="inlineStr"/>
       <c r="E758" t="inlineStr"/>
@@ -19849,16 +19849,16 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>VB020105-01-02-M-16</t>
+          <t>VB020202-01-02-M-09</t>
         </is>
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-M-ROJO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-M-BEIGE</t>
         </is>
       </c>
       <c r="C759" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D759" t="inlineStr"/>
       <c r="E759" t="inlineStr"/>
@@ -19871,12 +19871,12 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>VB020105-01-01-S-16</t>
+          <t>VB020202-01-02-M-02</t>
         </is>
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-S-ROJO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-M-NEGRO</t>
         </is>
       </c>
       <c r="C760" t="n">
@@ -19893,16 +19893,16 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>VB020204-01-03-L-08</t>
+          <t>VB020202-01-01-S-09</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-L-AZUL REY</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-S-BEIGE</t>
         </is>
       </c>
       <c r="C761" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D761" t="inlineStr"/>
       <c r="E761" t="inlineStr"/>
@@ -19915,16 +19915,16 @@
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>VB0103-01-01-S-32</t>
+          <t>VB020105-01-03-L-01</t>
         </is>
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-S-SELVA PAJAROS</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-L-BLANCO</t>
         </is>
       </c>
       <c r="C762" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D762" t="inlineStr"/>
       <c r="E762" t="inlineStr"/>
@@ -19937,16 +19937,16 @@
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>VB020204-01-03-L-07</t>
+          <t>VB020203-01-01-S-01</t>
         </is>
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-L-AZUL CIAN</t>
+          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-S-BLANCO</t>
         </is>
       </c>
       <c r="C763" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D763" t="inlineStr"/>
       <c r="E763" t="inlineStr"/>
@@ -19959,16 +19959,16 @@
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>VB020103-02-03-L-01</t>
+          <t>VB020105-01-01-S-01</t>
         </is>
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-L-BLANCO</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-S-BLANCO</t>
         </is>
       </c>
       <c r="C764" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D764" t="inlineStr"/>
       <c r="E764" t="inlineStr"/>
@@ -19981,16 +19981,16 @@
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>VB020204-01-03-L-15</t>
+          <t>VB0306-01-01-S-16</t>
         </is>
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-L-PURPURA</t>
+          <t>TOP BÁSICO LUISA-S-ROJO</t>
         </is>
       </c>
       <c r="C765" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D765" t="inlineStr"/>
       <c r="E765" t="inlineStr"/>
@@ -20003,16 +20003,16 @@
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>VB0103-01-03-L-32</t>
+          <t>VB0306-01-02-M-14</t>
         </is>
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-L-SELVA PAJAROS</t>
+          <t>TOP BÁSICO LUISA-M-PALO DE ROSA</t>
         </is>
       </c>
       <c r="C766" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D766" t="inlineStr"/>
       <c r="E766" t="inlineStr"/>
@@ -20025,16 +20025,16 @@
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>VB020202-01-03-L-23</t>
+          <t>VB0306-01-03-L-16</t>
         </is>
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-L-HOJAS AZUL</t>
+          <t>TOP BÁSICO LUISA-L-ROJO</t>
         </is>
       </c>
       <c r="C767" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D767" t="inlineStr"/>
       <c r="E767" t="inlineStr"/>
@@ -20047,16 +20047,16 @@
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>VB020202-01-01-S-23</t>
+          <t>VB0306-01-02-M-16</t>
         </is>
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-S-HOJAS AZUL</t>
+          <t>TOP BÁSICO LUISA-M-ROJO</t>
         </is>
       </c>
       <c r="C768" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D768" t="inlineStr"/>
       <c r="E768" t="inlineStr"/>
@@ -20069,16 +20069,16 @@
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>VB0103-01-02-M-32</t>
+          <t>VB0306-01-03-L-14</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-M-SELVA PAJAROS</t>
+          <t>TOP BÁSICO LUISA-L-PALO DE ROSA</t>
         </is>
       </c>
       <c r="C769" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D769" t="inlineStr"/>
       <c r="E769" t="inlineStr"/>
@@ -20091,16 +20091,16 @@
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>VB0302-01-02-M-01</t>
+          <t>VB0306-01-01-S-14</t>
         </is>
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-M-BLANCO</t>
+          <t>TOP BÁSICO LUISA-S-PALO DE ROSA</t>
         </is>
       </c>
       <c r="C770" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D770" t="inlineStr"/>
       <c r="E770" t="inlineStr"/>
@@ -20113,12 +20113,12 @@
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>VB0105-01-01-S-23</t>
+          <t>VB0103-01-03-L-01</t>
         </is>
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA-S-HOJAS AZUL</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-L-BLANCO</t>
         </is>
       </c>
       <c r="C771" t="n">
@@ -20135,16 +20135,16 @@
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>VB020204-01-03-L-13</t>
+          <t>VB0103-01-01-S-01</t>
         </is>
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-L-NARANJA</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-S-BLANCO</t>
         </is>
       </c>
       <c r="C772" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D772" t="inlineStr"/>
       <c r="E772" t="inlineStr"/>
@@ -20157,16 +20157,16 @@
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>VB020103-02-03-L-17</t>
+          <t>VB0103-01-01-S-02</t>
         </is>
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-L-ROSADO</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-S-NEGRO</t>
         </is>
       </c>
       <c r="C773" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D773" t="inlineStr"/>
       <c r="E773" t="inlineStr"/>
@@ -20179,16 +20179,16 @@
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>VB020103-02-02-M-17</t>
+          <t>VB0103-01-03-L-16</t>
         </is>
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-M-ROSADO</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-L-ROJO</t>
         </is>
       </c>
       <c r="C774" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D774" t="inlineStr"/>
       <c r="E774" t="inlineStr"/>
@@ -20201,16 +20201,16 @@
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-05</t>
+          <t>VB0103-01-02-M-16</t>
         </is>
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-AMARILLO NEON</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-M-ROJO</t>
         </is>
       </c>
       <c r="C775" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="D775" t="inlineStr"/>
       <c r="E775" t="inlineStr"/>
@@ -20223,16 +20223,16 @@
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>VB020303-01-01-S-26</t>
+          <t>VB0103-01-01-S-16</t>
         </is>
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-S-MISTICO</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-S-ROJO</t>
         </is>
       </c>
       <c r="C776" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="D776" t="inlineStr"/>
       <c r="E776" t="inlineStr"/>
@@ -20245,16 +20245,16 @@
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-13</t>
+          <t>VB020104-01-01-S-02</t>
         </is>
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-NARANJA</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-S-NEGRO</t>
         </is>
       </c>
       <c r="C777" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="D777" t="inlineStr"/>
       <c r="E777" t="inlineStr"/>
@@ -20267,16 +20267,16 @@
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>VB0302-01-03-L-01</t>
+          <t>VB020104-01-02-M-02</t>
         </is>
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-L-BLANCO</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-M-NEGRO</t>
         </is>
       </c>
       <c r="C778" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D778" t="inlineStr"/>
       <c r="E778" t="inlineStr"/>
@@ -20289,16 +20289,16 @@
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>VB020103-02-03-L-02</t>
+          <t>VB020104-01-03-L-02</t>
         </is>
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-L-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-L-NEGRO</t>
         </is>
       </c>
       <c r="C779" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D779" t="inlineStr"/>
       <c r="E779" t="inlineStr"/>
@@ -20311,16 +20311,16 @@
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>VB020204-01-02-M-07</t>
+          <t>VB020205-03-01-S-21</t>
         </is>
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-M-AZUL CIAN</t>
+          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-S-ASTRAL</t>
         </is>
       </c>
       <c r="C780" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D780" t="inlineStr"/>
       <c r="E780" t="inlineStr"/>
@@ -20333,16 +20333,16 @@
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-08</t>
+          <t>VB020205-03-02-M-21</t>
         </is>
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-AZUL REY</t>
+          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-M-ASTRAL</t>
         </is>
       </c>
       <c r="C781" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D781" t="inlineStr"/>
       <c r="E781" t="inlineStr"/>
@@ -20355,16 +20355,16 @@
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>VB0302-01-03-L-02</t>
+          <t>VB020205-03-03-L-21</t>
         </is>
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-L-NEGRO</t>
+          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-L-ASTRAL</t>
         </is>
       </c>
       <c r="C782" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="D782" t="inlineStr"/>
       <c r="E782" t="inlineStr"/>
@@ -20377,16 +20377,16 @@
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-11</t>
+          <t>VB020205-02-03-L-04</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-FUCSIA NEON</t>
+          <t>VB DOS PIEZAS TOP TANGA-L-AMARILLO</t>
         </is>
       </c>
       <c r="C783" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D783" t="inlineStr"/>
       <c r="E783" t="inlineStr"/>
@@ -20399,16 +20399,16 @@
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>VB020103-02-01-S-17</t>
+          <t>VB020205-02-03-L-07</t>
         </is>
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-S-ROSADO</t>
+          <t>VB DOS PIEZAS TOP TANGA-L-AZUL CIAN</t>
         </is>
       </c>
       <c r="C784" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D784" t="inlineStr"/>
       <c r="E784" t="inlineStr"/>
@@ -20421,16 +20421,16 @@
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>VB0302-01-01-S-01</t>
+          <t>VB020205-02-03-L-22</t>
         </is>
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-S-BLANCO</t>
+          <t>VB DOS PIEZAS TOP TANGA-L-FLORES</t>
         </is>
       </c>
       <c r="C785" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="D785" t="inlineStr"/>
       <c r="E785" t="inlineStr"/>
@@ -20443,16 +20443,16 @@
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>VB0105-01-02-M-23</t>
+          <t>VB020205-02-03-L-10</t>
         </is>
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA-M-HOJAS AZUL</t>
+          <t>VB DOS PIEZAS TOP TANGA-L-FUCSIA</t>
         </is>
       </c>
       <c r="C786" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D786" t="inlineStr"/>
       <c r="E786" t="inlineStr"/>
@@ -20465,16 +20465,16 @@
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>VB020204-01-03-L-11</t>
+          <t>VB020205-02-03-L-12</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-L-FUCSIA NEON</t>
+          <t>VB DOS PIEZAS TOP TANGA-L-MORADO</t>
         </is>
       </c>
       <c r="C787" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D787" t="inlineStr"/>
       <c r="E787" t="inlineStr"/>
@@ -20487,16 +20487,16 @@
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>VB020103-02-03-L-03</t>
+          <t>VB020205-02-02-M-04</t>
         </is>
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-L-AGUAMARINA</t>
+          <t>VB DOS PIEZAS TOP TANGA-M-AMARILLO</t>
         </is>
       </c>
       <c r="C788" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D788" t="inlineStr"/>
       <c r="E788" t="inlineStr"/>
@@ -20509,16 +20509,16 @@
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>VB020103-02-01-S-03</t>
+          <t>VB020205-02-02-M-07</t>
         </is>
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-S-AGUAMARINA</t>
+          <t>VB DOS PIEZAS TOP TANGA-M-AZUL CIAN</t>
         </is>
       </c>
       <c r="C789" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D789" t="inlineStr"/>
       <c r="E789" t="inlineStr"/>
@@ -20531,16 +20531,16 @@
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>VB020103-02-02-M-03</t>
+          <t>VB020205-02-02-M-22</t>
         </is>
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-M-AGUAMARINA</t>
+          <t>VB DOS PIEZAS TOP TANGA-M-FLORES</t>
         </is>
       </c>
       <c r="C790" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D790" t="inlineStr"/>
       <c r="E790" t="inlineStr"/>
@@ -20553,16 +20553,16 @@
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>VB020103-02-01-S-02</t>
+          <t>VB020205-02-01-S-04</t>
         </is>
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-S-NEGRO</t>
+          <t>VB DOS PIEZAS TOP TANGA-S-AMARILLO</t>
         </is>
       </c>
       <c r="C791" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="D791" t="inlineStr"/>
       <c r="E791" t="inlineStr"/>
@@ -20575,16 +20575,16 @@
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>VB020204-01-02-M-13</t>
+          <t>VB020205-02-01-S-07</t>
         </is>
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-M-NARANJA</t>
+          <t>VB DOS PIEZAS TOP TANGA-S-AZUL CIAN</t>
         </is>
       </c>
       <c r="C792" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D792" t="inlineStr"/>
       <c r="E792" t="inlineStr"/>
@@ -20597,16 +20597,16 @@
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-07</t>
+          <t>VB020205-02-01-S-22</t>
         </is>
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-AZUL CIAN</t>
+          <t>VB DOS PIEZAS TOP TANGA-S-FLORES</t>
         </is>
       </c>
       <c r="C793" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="D793" t="inlineStr"/>
       <c r="E793" t="inlineStr"/>
@@ -20619,16 +20619,16 @@
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>VB020204-01-02-M-11</t>
+          <t>VB020205-02-01-S-10</t>
         </is>
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-M-FUCSIA NEON</t>
+          <t>VB DOS PIEZAS TOP TANGA-S-FUCSIA</t>
         </is>
       </c>
       <c r="C794" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D794" t="inlineStr"/>
       <c r="E794" t="inlineStr"/>
@@ -20641,16 +20641,16 @@
     <row r="795">
       <c r="A795" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-15</t>
+          <t>VB020205-02-01-S-12</t>
         </is>
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-PURPURA</t>
+          <t>VB DOS PIEZAS TOP TANGA-S-MORADO</t>
         </is>
       </c>
       <c r="C795" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D795" t="inlineStr"/>
       <c r="E795" t="inlineStr"/>
@@ -20663,16 +20663,16 @@
     <row r="796">
       <c r="A796" t="inlineStr">
         <is>
-          <t>VB020303-01-03-L-26</t>
+          <t>VB020202-01-03-L-04</t>
         </is>
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-L-MISTICO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-L-AMARILLO</t>
         </is>
       </c>
       <c r="C796" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="D796" t="inlineStr"/>
       <c r="E796" t="inlineStr"/>
@@ -20685,16 +20685,16 @@
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t>VB020303-01-02-M-26</t>
+          <t>VB020202-01-03-L-08</t>
         </is>
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-M-MISTICO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-L-AZUL REY</t>
         </is>
       </c>
       <c r="C797" t="n">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="D797" t="inlineStr"/>
       <c r="E797" t="inlineStr"/>
@@ -20707,16 +20707,16 @@
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>VB020204-01-02-M-08</t>
+          <t>VB020202-01-03-L-19</t>
         </is>
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-M-AZUL REY</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-L-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C798" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D798" t="inlineStr"/>
       <c r="E798" t="inlineStr"/>
@@ -20729,16 +20729,16 @@
     <row r="799">
       <c r="A799" t="inlineStr">
         <is>
-          <t>VB020202-01-02-M-23</t>
+          <t>VB020202-01-03-L-22</t>
         </is>
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-M-HOJAS AZUL</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-L-FLORES</t>
         </is>
       </c>
       <c r="C799" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D799" t="inlineStr"/>
       <c r="E799" t="inlineStr"/>
@@ -20751,16 +20751,16 @@
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>VB0105-01-03-L-23</t>
+          <t>VB020202-01-02-M-04</t>
         </is>
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA-L-HOJAS AZUL</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-M-AMARILLO</t>
         </is>
       </c>
       <c r="C800" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D800" t="inlineStr"/>
       <c r="E800" t="inlineStr"/>
@@ -20773,16 +20773,16 @@
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>VB020203-01-03-L-01</t>
+          <t>VB020202-01-02-M-08</t>
         </is>
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-L-BLANCO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-M-AZUL REY</t>
         </is>
       </c>
       <c r="C801" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="D801" t="inlineStr"/>
       <c r="E801" t="inlineStr"/>
@@ -20795,16 +20795,16 @@
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>VB020203-01-02-M-01</t>
+          <t>VB020202-01-02-M-19</t>
         </is>
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-M-BLANCO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-M-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C802" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D802" t="inlineStr"/>
       <c r="E802" t="inlineStr"/>
@@ -20817,16 +20817,16 @@
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>VB0302-01-02-M-02</t>
+          <t>VB020202-01-02-M-22</t>
         </is>
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-M-NEGRO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-M-FLORES</t>
         </is>
       </c>
       <c r="C803" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="D803" t="inlineStr"/>
       <c r="E803" t="inlineStr"/>
@@ -20839,16 +20839,16 @@
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t>VB020204-01-02-M-05</t>
+          <t>VB020202-01-01-S-04</t>
         </is>
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-M-AMARILLO NEON</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-S-AMARILLO</t>
         </is>
       </c>
       <c r="C804" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="D804" t="inlineStr"/>
       <c r="E804" t="inlineStr"/>
@@ -20861,16 +20861,16 @@
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>VB020202-01-03-L-07</t>
+          <t>VB020202-01-01-S-08</t>
         </is>
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-L-AZUL CIAN</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-S-AZUL REY</t>
         </is>
       </c>
       <c r="C805" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D805" t="inlineStr"/>
       <c r="E805" t="inlineStr"/>
@@ -20883,12 +20883,12 @@
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>VB020202-01-02-M-07</t>
+          <t>VB020202-01-01-S-19</t>
         </is>
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-M-AZUL CIAN</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-S-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C806" t="n">
@@ -20905,12 +20905,12 @@
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>VB020202-01-01-S-07</t>
+          <t>VB020202-01-01-S-22</t>
         </is>
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-S-AZUL CIAN</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-S-FLORES</t>
         </is>
       </c>
       <c r="C807" t="n">
@@ -20927,16 +20927,16 @@
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>VB020101-01-01-S-15</t>
+          <t>VB0105-01-01-S-31</t>
         </is>
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-PURPURA</t>
+          <t>VB ENTERO TANGA-S-SAFARI</t>
         </is>
       </c>
       <c r="C808" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D808" t="inlineStr"/>
       <c r="E808" t="inlineStr"/>
@@ -20949,16 +20949,16 @@
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>VB020105-01-02-M-01</t>
+          <t>VB0105-01-02-M-31</t>
         </is>
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-M-BLANCO</t>
+          <t>VB ENTERO TANGA-M-SAFARI</t>
         </is>
       </c>
       <c r="C809" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D809" t="inlineStr"/>
       <c r="E809" t="inlineStr"/>
@@ -20971,16 +20971,16 @@
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>VB020203-01-03-L-02</t>
+          <t>VB0105-01-03-L-31</t>
         </is>
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-L-NEGRO</t>
+          <t>VB ENTERO TANGA-L-SAFARI</t>
         </is>
       </c>
       <c r="C810" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D810" t="inlineStr"/>
       <c r="E810" t="inlineStr"/>
@@ -20993,16 +20993,16 @@
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>VB020202-01-03-L-02</t>
+          <t>VB020402-01-01-S-31</t>
         </is>
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-L-NEGRO</t>
+          <t>VB DOS PIEZAS BUSO TALLE ALTO-S-SAFARI</t>
         </is>
       </c>
       <c r="C811" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D811" t="inlineStr"/>
       <c r="E811" t="inlineStr"/>
@@ -21015,16 +21015,16 @@
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>VB020202-01-01-S-02</t>
+          <t>VB020402-01-02-M-31</t>
         </is>
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-S-NEGRO</t>
+          <t>VB DOS PIEZAS BUSO TALLE ALTO-M-SAFARI</t>
         </is>
       </c>
       <c r="C812" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="D812" t="inlineStr"/>
       <c r="E812" t="inlineStr"/>
@@ -21037,16 +21037,16 @@
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>VB020202-01-03-L-09</t>
+          <t>VB020101-01-01-S-05</t>
         </is>
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-L-BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C813" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="D813" t="inlineStr"/>
       <c r="E813" t="inlineStr"/>
@@ -21059,16 +21059,16 @@
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>VB020202-01-02-M-09</t>
+          <t>VB020101-01-02-M-05</t>
         </is>
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-M-BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C814" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D814" t="inlineStr"/>
       <c r="E814" t="inlineStr"/>
@@ -21081,16 +21081,16 @@
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>VB020202-01-02-M-02</t>
+          <t>VB020101-01-03-L-05</t>
         </is>
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-M-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C815" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D815" t="inlineStr"/>
       <c r="E815" t="inlineStr"/>
@@ -21103,16 +21103,16 @@
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t>VB020202-01-01-S-09</t>
+          <t>VB020101-01-03-L-27</t>
         </is>
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-S-BEIGE</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-PITON AZUL</t>
         </is>
       </c>
       <c r="C816" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="D816" t="inlineStr"/>
       <c r="E816" t="inlineStr"/>
@@ -21125,16 +21125,16 @@
     <row r="817">
       <c r="A817" t="inlineStr">
         <is>
-          <t>VB020105-01-03-L-01</t>
+          <t>VB020101-01-01-S-29</t>
         </is>
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-L-BLANCO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-PITON ROSADO</t>
         </is>
       </c>
       <c r="C817" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D817" t="inlineStr"/>
       <c r="E817" t="inlineStr"/>
@@ -21147,16 +21147,16 @@
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
-          <t>VB020203-01-01-S-01</t>
+          <t>VB020101-01-02-M-29</t>
         </is>
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-S-BLANCO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-PITON ROSADO</t>
         </is>
       </c>
       <c r="C818" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D818" t="inlineStr"/>
       <c r="E818" t="inlineStr"/>
@@ -21169,16 +21169,16 @@
     <row r="819">
       <c r="A819" t="inlineStr">
         <is>
-          <t>VB020105-01-01-S-01</t>
+          <t>VB020101-01-03-L-29</t>
         </is>
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-S-BLANCO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-PITON ROSADO</t>
         </is>
       </c>
       <c r="C819" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D819" t="inlineStr"/>
       <c r="E819" t="inlineStr"/>
@@ -22215,16 +22215,16 @@
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>160805</t>
+          <t>370602</t>
         </is>
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>FRAGANCIA COCO PASION</t>
+          <t>TWIN 80</t>
         </is>
       </c>
       <c r="C860" t="n">
-        <v>134</v>
+        <v>108400</v>
       </c>
       <c r="D860" t="inlineStr"/>
       <c r="E860" t="inlineStr">
@@ -22241,16 +22241,16 @@
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>370602</t>
+          <t>160805</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>TWIN 80</t>
+          <t>FRAGANCIA COCO PASION</t>
         </is>
       </c>
       <c r="C861" t="n">
-        <v>108400</v>
+        <v>134</v>
       </c>
       <c r="D861" t="inlineStr"/>
       <c r="E861" t="inlineStr">
@@ -23879,16 +23879,16 @@
     <row r="924">
       <c r="A924" t="inlineStr">
         <is>
-          <t>340903</t>
+          <t>370105</t>
         </is>
       </c>
       <c r="B924" t="inlineStr">
         <is>
-          <t>PULLULAN</t>
+          <t>TRIETANOLAMINA</t>
         </is>
       </c>
       <c r="C924" t="n">
-        <v>74420</v>
+        <v>1002300</v>
       </c>
       <c r="D924" t="inlineStr"/>
       <c r="E924" t="inlineStr">
@@ -23905,16 +23905,16 @@
     <row r="925">
       <c r="A925" t="inlineStr">
         <is>
-          <t>160822</t>
+          <t>340903</t>
         </is>
       </c>
       <c r="B925" t="inlineStr">
         <is>
-          <t>FRAGANCIA WATERY FRUITS</t>
+          <t>PULLULAN</t>
         </is>
       </c>
       <c r="C925" t="n">
-        <v>31510</v>
+        <v>74420</v>
       </c>
       <c r="D925" t="inlineStr"/>
       <c r="E925" t="inlineStr">
@@ -23931,16 +23931,16 @@
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
-          <t>160814</t>
+          <t>160822</t>
         </is>
       </c>
       <c r="B926" t="inlineStr">
         <is>
-          <t>FRAGANCIA ORANGE</t>
+          <t>FRAGANCIA WATERY FRUITS</t>
         </is>
       </c>
       <c r="C926" t="n">
-        <v>6880</v>
+        <v>31510</v>
       </c>
       <c r="D926" t="inlineStr"/>
       <c r="E926" t="inlineStr">
@@ -23957,16 +23957,16 @@
     <row r="927">
       <c r="A927" t="inlineStr">
         <is>
-          <t>370105</t>
+          <t>160814</t>
         </is>
       </c>
       <c r="B927" t="inlineStr">
         <is>
-          <t>TRIETANOLAMINA</t>
+          <t>FRAGANCIA ORANGE</t>
         </is>
       </c>
       <c r="C927" t="n">
-        <v>1002300</v>
+        <v>6880</v>
       </c>
       <c r="D927" t="inlineStr"/>
       <c r="E927" t="inlineStr">
@@ -24815,16 +24815,16 @@
     <row r="960">
       <c r="A960" t="inlineStr">
         <is>
-          <t>354301</t>
+          <t>380103</t>
         </is>
       </c>
       <c r="B960" t="inlineStr">
         <is>
-          <t>AMIDET N</t>
+          <t>DIOXIDO DE TITANIO</t>
         </is>
       </c>
       <c r="C960" t="n">
-        <v>76980</v>
+        <v>62700</v>
       </c>
       <c r="D960" t="inlineStr"/>
       <c r="E960" t="inlineStr">
@@ -24841,16 +24841,16 @@
     <row r="961">
       <c r="A961" t="inlineStr">
         <is>
-          <t>380103</t>
+          <t>354301</t>
         </is>
       </c>
       <c r="B961" t="inlineStr">
         <is>
-          <t>DIOXIDO DE TITANIO</t>
+          <t>AMIDET N</t>
         </is>
       </c>
       <c r="C961" t="n">
-        <v>62700</v>
+        <v>76980</v>
       </c>
       <c r="D961" t="inlineStr"/>
       <c r="E961" t="inlineStr">
@@ -25621,16 +25621,16 @@
     <row r="991">
       <c r="A991" t="inlineStr">
         <is>
-          <t>144602</t>
+          <t>360302</t>
         </is>
       </c>
       <c r="B991" t="inlineStr">
         <is>
-          <t>EMULIUM DELTA MB</t>
+          <t>360302</t>
         </is>
       </c>
       <c r="C991" t="n">
-        <v>212360</v>
+        <v>135600</v>
       </c>
       <c r="D991" t="inlineStr"/>
       <c r="E991" t="inlineStr">
@@ -25647,16 +25647,16 @@
     <row r="992">
       <c r="A992" t="inlineStr">
         <is>
-          <t>360302</t>
+          <t>144602</t>
         </is>
       </c>
       <c r="B992" t="inlineStr">
         <is>
-          <t>360302</t>
+          <t>EMULIUM DELTA MB</t>
         </is>
       </c>
       <c r="C992" t="n">
-        <v>135600</v>
+        <v>212360</v>
       </c>
       <c r="D992" t="inlineStr"/>
       <c r="E992" t="inlineStr">
@@ -25751,21 +25751,21 @@
     <row r="996">
       <c r="A996" t="inlineStr">
         <is>
-          <t>144301</t>
+          <t>ET0203VG</t>
         </is>
       </c>
       <c r="B996" t="inlineStr">
         <is>
-          <t>ALCOHOL CETOESTEARÍLICO 30/70</t>
+          <t>ETIQUETA LIP GLOSS VIVIANA GRONDONA D1</t>
         </is>
       </c>
       <c r="C996" t="n">
-        <v>155440</v>
+        <v>9704</v>
       </c>
       <c r="D996" t="inlineStr"/>
       <c r="E996" t="inlineStr">
         <is>
-          <t>MATERIA PRIMA</t>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
         </is>
       </c>
       <c r="F996" t="inlineStr">
@@ -25777,16 +25777,16 @@
     <row r="997">
       <c r="A997" t="inlineStr">
         <is>
-          <t>ET0203VG</t>
+          <t>ET0204VG</t>
         </is>
       </c>
       <c r="B997" t="inlineStr">
         <is>
-          <t>ETIQUETA LIP GLOSS VIVIANA GRONDONA D1</t>
+          <t>ETIQUETA LIP GLOSS VIVIANA GRONDONA D2</t>
         </is>
       </c>
       <c r="C997" t="n">
-        <v>9704</v>
+        <v>9605</v>
       </c>
       <c r="D997" t="inlineStr"/>
       <c r="E997" t="inlineStr">
@@ -25803,21 +25803,21 @@
     <row r="998">
       <c r="A998" t="inlineStr">
         <is>
-          <t>ET0204VG</t>
+          <t>144301</t>
         </is>
       </c>
       <c r="B998" t="inlineStr">
         <is>
-          <t>ETIQUETA LIP GLOSS VIVIANA GRONDONA D2</t>
+          <t>ALCOHOL CETOESTEARÍLICO 30/70</t>
         </is>
       </c>
       <c r="C998" t="n">
-        <v>9605</v>
+        <v>155440</v>
       </c>
       <c r="D998" t="inlineStr"/>
       <c r="E998" t="inlineStr">
         <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+          <t>MATERIA PRIMA</t>
         </is>
       </c>
       <c r="F998" t="inlineStr">
@@ -26193,16 +26193,16 @@
     <row r="1013">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>244503</t>
+          <t>360303</t>
         </is>
       </c>
       <c r="B1013" t="inlineStr">
         <is>
-          <t>244503</t>
+          <t>360303</t>
         </is>
       </c>
       <c r="C1013" t="n">
-        <v>87900</v>
+        <v>8160</v>
       </c>
       <c r="D1013" t="inlineStr"/>
       <c r="E1013" t="inlineStr">
@@ -26219,16 +26219,16 @@
     <row r="1014">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>360303</t>
+          <t>244503</t>
         </is>
       </c>
       <c r="B1014" t="inlineStr">
         <is>
-          <t>360303</t>
+          <t>244503</t>
         </is>
       </c>
       <c r="C1014" t="n">
-        <v>8160</v>
+        <v>87900</v>
       </c>
       <c r="D1014" t="inlineStr"/>
       <c r="E1014" t="inlineStr">
@@ -26869,16 +26869,16 @@
     <row r="1039">
       <c r="A1039" t="inlineStr">
         <is>
-          <t>350106</t>
+          <t>384701</t>
         </is>
       </c>
       <c r="B1039" t="inlineStr">
         <is>
-          <t>PROAMIDE CR/COCOAMIDA</t>
+          <t>FRESCOLAT® ML CRYST.</t>
         </is>
       </c>
       <c r="C1039" t="n">
-        <v>1200000</v>
+        <v>1200</v>
       </c>
       <c r="D1039" t="inlineStr"/>
       <c r="E1039" t="inlineStr">
@@ -26895,16 +26895,16 @@
     <row r="1040">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>384701</t>
+          <t>350106</t>
         </is>
       </c>
       <c r="B1040" t="inlineStr">
         <is>
-          <t>FRESCOLAT® ML CRYST.</t>
+          <t>PROAMIDE CR/COCOAMIDA</t>
         </is>
       </c>
       <c r="C1040" t="n">
-        <v>1200</v>
+        <v>1200000</v>
       </c>
       <c r="D1040" t="inlineStr"/>
       <c r="E1040" t="inlineStr">
@@ -27337,16 +27337,16 @@
     <row r="1057">
       <c r="A1057" t="inlineStr">
         <is>
-          <t>174402</t>
+          <t>370603</t>
         </is>
       </c>
       <c r="B1057" t="inlineStr">
         <is>
-          <t>174402</t>
+          <t>CLORURO DE SODIO</t>
         </is>
       </c>
       <c r="C1057" t="n">
-        <v>3536</v>
+        <v>33240</v>
       </c>
       <c r="D1057" t="inlineStr"/>
       <c r="E1057" t="inlineStr">
@@ -27363,16 +27363,16 @@
     <row r="1058">
       <c r="A1058" t="inlineStr">
         <is>
-          <t>344001</t>
+          <t>174402</t>
         </is>
       </c>
       <c r="B1058" t="inlineStr">
         <is>
-          <t>344001</t>
+          <t>174402</t>
         </is>
       </c>
       <c r="C1058" t="n">
-        <v>53115</v>
+        <v>3536</v>
       </c>
       <c r="D1058" t="inlineStr"/>
       <c r="E1058" t="inlineStr">
@@ -27389,16 +27389,16 @@
     <row r="1059">
       <c r="A1059" t="inlineStr">
         <is>
-          <t>370603</t>
+          <t>344001</t>
         </is>
       </c>
       <c r="B1059" t="inlineStr">
         <is>
-          <t>CLORURO DE SODIO</t>
+          <t>344001</t>
         </is>
       </c>
       <c r="C1059" t="n">
-        <v>33240</v>
+        <v>53115</v>
       </c>
       <c r="D1059" t="inlineStr"/>
       <c r="E1059" t="inlineStr">
@@ -28273,16 +28273,16 @@
     <row r="1093">
       <c r="A1093" t="inlineStr">
         <is>
-          <t>110101</t>
+          <t>385101</t>
         </is>
       </c>
       <c r="B1093" t="inlineStr">
         <is>
-          <t>ACEITE DE AGUACATE HIDROLIZADO</t>
+          <t>GRANSIL PSQ</t>
         </is>
       </c>
       <c r="C1093" t="n">
-        <v>1600</v>
+        <v>80</v>
       </c>
       <c r="D1093" t="inlineStr"/>
       <c r="E1093" t="inlineStr">
@@ -28299,16 +28299,16 @@
     <row r="1094">
       <c r="A1094" t="inlineStr">
         <is>
-          <t>385101</t>
+          <t>110101</t>
         </is>
       </c>
       <c r="B1094" t="inlineStr">
         <is>
-          <t>GRANSIL PSQ</t>
+          <t>ACEITE DE AGUACATE HIDROLIZADO</t>
         </is>
       </c>
       <c r="C1094" t="n">
-        <v>80</v>
+        <v>1600</v>
       </c>
       <c r="D1094" t="inlineStr"/>
       <c r="E1094" t="inlineStr">
@@ -29183,21 +29183,21 @@
     <row r="1128">
       <c r="A1128" t="inlineStr">
         <is>
-          <t>314208</t>
+          <t>ME1049</t>
         </is>
       </c>
       <c r="B1128" t="inlineStr">
         <is>
-          <t>GEMTONE AMBER G001</t>
+          <t>TAPA PUSH PULL DORADA ROSCA 24</t>
         </is>
       </c>
       <c r="C1128" t="n">
-        <v>73488</v>
+        <v>3386</v>
       </c>
       <c r="D1128" t="inlineStr"/>
       <c r="E1128" t="inlineStr">
         <is>
-          <t>MATERIA PRIMA</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1128" t="inlineStr">
@@ -29209,21 +29209,21 @@
     <row r="1129">
       <c r="A1129" t="inlineStr">
         <is>
-          <t>ME1049</t>
+          <t>314208</t>
         </is>
       </c>
       <c r="B1129" t="inlineStr">
         <is>
-          <t>TAPA PUSH PULL DORADA ROSCA 24</t>
+          <t>GEMTONE AMBER G001</t>
         </is>
       </c>
       <c r="C1129" t="n">
-        <v>3386</v>
+        <v>73488</v>
       </c>
       <c r="D1129" t="inlineStr"/>
       <c r="E1129" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIA PRIMA</t>
         </is>
       </c>
       <c r="F1129" t="inlineStr">
@@ -30665,21 +30665,21 @@
     <row r="1185">
       <c r="A1185" t="inlineStr">
         <is>
-          <t>173501</t>
+          <t>ME1044</t>
         </is>
       </c>
       <c r="B1185" t="inlineStr">
         <is>
-          <t>ULTRAMAR U-200 AZUL</t>
+          <t>TAPA FLIP TOP PLATEADA ROSCA 18</t>
         </is>
       </c>
       <c r="C1185" t="n">
-        <v>4210</v>
+        <v>39166</v>
       </c>
       <c r="D1185" t="inlineStr"/>
       <c r="E1185" t="inlineStr">
         <is>
-          <t>MATERIA PRIMA</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1185" t="inlineStr">
@@ -30691,21 +30691,21 @@
     <row r="1186">
       <c r="A1186" t="inlineStr">
         <is>
-          <t>ME1044</t>
+          <t>173501</t>
         </is>
       </c>
       <c r="B1186" t="inlineStr">
         <is>
-          <t>TAPA FLIP TOP PLATEADA ROSCA 18</t>
+          <t>ULTRAMAR U-200 AZUL</t>
         </is>
       </c>
       <c r="C1186" t="n">
-        <v>39166</v>
+        <v>4210</v>
       </c>
       <c r="D1186" t="inlineStr"/>
       <c r="E1186" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIA PRIMA</t>
         </is>
       </c>
       <c r="F1186" t="inlineStr">
@@ -34587,21 +34587,21 @@
     <row r="1336">
       <c r="A1336" t="inlineStr">
         <is>
-          <t>314202</t>
+          <t>ME0527</t>
         </is>
       </c>
       <c r="B1336" t="inlineStr">
         <is>
-          <t>CLOISONNE ROUGE FLAMBE 440X</t>
+          <t>ENVASE VIDRIO ROSADO MARCADO 30ML</t>
         </is>
       </c>
       <c r="C1336" t="n">
-        <v>6266</v>
+        <v>46</v>
       </c>
       <c r="D1336" t="inlineStr"/>
       <c r="E1336" t="inlineStr">
         <is>
-          <t>MATERIA PRIMA</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1336" t="inlineStr">
@@ -34613,21 +34613,21 @@
     <row r="1337">
       <c r="A1337" t="inlineStr">
         <is>
-          <t>ME0527</t>
+          <t>314202</t>
         </is>
       </c>
       <c r="B1337" t="inlineStr">
         <is>
-          <t>ENVASE VIDRIO ROSADO MARCADO 30ML</t>
+          <t>CLOISONNE ROUGE FLAMBE 440X</t>
         </is>
       </c>
       <c r="C1337" t="n">
-        <v>46</v>
+        <v>6266</v>
       </c>
       <c r="D1337" t="inlineStr"/>
       <c r="E1337" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIA PRIMA</t>
         </is>
       </c>
       <c r="F1337" t="inlineStr">
@@ -34873,21 +34873,21 @@
     <row r="1347">
       <c r="A1347" t="inlineStr">
         <is>
-          <t>190102</t>
+          <t>ET0202CA</t>
         </is>
       </c>
       <c r="B1347" t="inlineStr">
         <is>
-          <t>CARBÓN ACTIVADO</t>
+          <t>ETIQUETA ILUMINADOR GOLD ROSE CARA</t>
         </is>
       </c>
       <c r="C1347" t="n">
-        <v>500</v>
+        <v>3916</v>
       </c>
       <c r="D1347" t="inlineStr"/>
       <c r="E1347" t="inlineStr">
         <is>
-          <t>MATERIA PRIMA</t>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
         </is>
       </c>
       <c r="F1347" t="inlineStr">
@@ -34899,21 +34899,21 @@
     <row r="1348">
       <c r="A1348" t="inlineStr">
         <is>
-          <t>ET0202CA</t>
+          <t>190102</t>
         </is>
       </c>
       <c r="B1348" t="inlineStr">
         <is>
-          <t>ETIQUETA ILUMINADOR GOLD ROSE CARA</t>
+          <t>CARBÓN ACTIVADO</t>
         </is>
       </c>
       <c r="C1348" t="n">
-        <v>3916</v>
+        <v>500</v>
       </c>
       <c r="D1348" t="inlineStr"/>
       <c r="E1348" t="inlineStr">
         <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+          <t>MATERIA PRIMA</t>
         </is>
       </c>
       <c r="F1348" t="inlineStr">
@@ -38967,16 +38967,16 @@
     <row r="1504">
       <c r="A1504" t="inlineStr">
         <is>
-          <t>250301</t>
+          <t>360109</t>
         </is>
       </c>
       <c r="B1504" t="inlineStr">
         <is>
-          <t>250301</t>
+          <t>CELQUAT SC 230</t>
         </is>
       </c>
       <c r="C1504" t="n">
-        <v>8</v>
+        <v>11560</v>
       </c>
       <c r="D1504" t="inlineStr"/>
       <c r="E1504" t="inlineStr">
@@ -38993,16 +38993,16 @@
     <row r="1505">
       <c r="A1505" t="inlineStr">
         <is>
-          <t>360109</t>
+          <t>250301</t>
         </is>
       </c>
       <c r="B1505" t="inlineStr">
         <is>
-          <t>CELQUAT SC 230</t>
+          <t>250301</t>
         </is>
       </c>
       <c r="C1505" t="n">
-        <v>11560</v>
+        <v>8</v>
       </c>
       <c r="D1505" t="inlineStr"/>
       <c r="E1505" t="inlineStr">
@@ -39227,16 +39227,16 @@
     <row r="1514">
       <c r="A1514" t="inlineStr">
         <is>
-          <t>300302</t>
+          <t>360301</t>
         </is>
       </c>
       <c r="B1514" t="inlineStr">
         <is>
-          <t>300302</t>
+          <t>360301</t>
         </is>
       </c>
       <c r="C1514" t="n">
-        <v>264</v>
+        <v>121920</v>
       </c>
       <c r="D1514" t="inlineStr"/>
       <c r="E1514" t="inlineStr">
@@ -39253,16 +39253,16 @@
     <row r="1515">
       <c r="A1515" t="inlineStr">
         <is>
-          <t>360301</t>
+          <t>300302</t>
         </is>
       </c>
       <c r="B1515" t="inlineStr">
         <is>
-          <t>360301</t>
+          <t>300302</t>
         </is>
       </c>
       <c r="C1515" t="n">
-        <v>121920</v>
+        <v>264</v>
       </c>
       <c r="D1515" t="inlineStr"/>
       <c r="E1515" t="inlineStr">
@@ -39435,16 +39435,16 @@
     <row r="1522">
       <c r="A1522" t="inlineStr">
         <is>
-          <t>340903</t>
+          <t>370105</t>
         </is>
       </c>
       <c r="B1522" t="inlineStr">
         <is>
-          <t>PULLULAN</t>
+          <t>TRIETANOLAMINA</t>
         </is>
       </c>
       <c r="C1522" t="n">
-        <v>146</v>
+        <v>49450</v>
       </c>
       <c r="D1522" t="inlineStr"/>
       <c r="E1522" t="inlineStr">
@@ -39461,16 +39461,16 @@
     <row r="1523">
       <c r="A1523" t="inlineStr">
         <is>
-          <t>160814</t>
+          <t>340903</t>
         </is>
       </c>
       <c r="B1523" t="inlineStr">
         <is>
-          <t>FRAGANCIA ORANGE</t>
+          <t>PULLULAN</t>
         </is>
       </c>
       <c r="C1523" t="n">
-        <v>320</v>
+        <v>146</v>
       </c>
       <c r="D1523" t="inlineStr"/>
       <c r="E1523" t="inlineStr">
@@ -39487,16 +39487,16 @@
     <row r="1524">
       <c r="A1524" t="inlineStr">
         <is>
-          <t>140103</t>
+          <t>160814</t>
         </is>
       </c>
       <c r="B1524" t="inlineStr">
         <is>
-          <t>ALCOHOL ESTEARÍLICO</t>
+          <t>FRAGANCIA ORANGE</t>
         </is>
       </c>
       <c r="C1524" t="n">
-        <v>334300</v>
+        <v>320</v>
       </c>
       <c r="D1524" t="inlineStr"/>
       <c r="E1524" t="inlineStr">
@@ -39513,16 +39513,16 @@
     <row r="1525">
       <c r="A1525" t="inlineStr">
         <is>
-          <t>370105</t>
+          <t>140103</t>
         </is>
       </c>
       <c r="B1525" t="inlineStr">
         <is>
-          <t>TRIETANOLAMINA</t>
+          <t>ALCOHOL ESTEARÍLICO</t>
         </is>
       </c>
       <c r="C1525" t="n">
-        <v>49450</v>
+        <v>334300</v>
       </c>
       <c r="D1525" t="inlineStr"/>
       <c r="E1525" t="inlineStr">
@@ -39591,16 +39591,16 @@
     <row r="1528">
       <c r="A1528" t="inlineStr">
         <is>
-          <t>320103</t>
+          <t>370106</t>
         </is>
       </c>
       <c r="B1528" t="inlineStr">
         <is>
-          <t>VITAMINA E ACETATO</t>
+          <t>ÁCIDO LÁCTICO AL 88%</t>
         </is>
       </c>
       <c r="C1528" t="n">
-        <v>15300</v>
+        <v>36610</v>
       </c>
       <c r="D1528" t="inlineStr"/>
       <c r="E1528" t="inlineStr">
@@ -39617,16 +39617,16 @@
     <row r="1529">
       <c r="A1529" t="inlineStr">
         <is>
-          <t>370106</t>
+          <t>320103</t>
         </is>
       </c>
       <c r="B1529" t="inlineStr">
         <is>
-          <t>ÁCIDO LÁCTICO AL 88%</t>
+          <t>VITAMINA E ACETATO</t>
         </is>
       </c>
       <c r="C1529" t="n">
-        <v>36610</v>
+        <v>15300</v>
       </c>
       <c r="D1529" t="inlineStr"/>
       <c r="E1529" t="inlineStr">
@@ -40033,16 +40033,16 @@
     <row r="1545">
       <c r="A1545" t="inlineStr">
         <is>
-          <t>354301</t>
+          <t>380103</t>
         </is>
       </c>
       <c r="B1545" t="inlineStr">
         <is>
-          <t>AMIDET N</t>
+          <t>DIOXIDO DE TITANIO</t>
         </is>
       </c>
       <c r="C1545" t="n">
-        <v>17900</v>
+        <v>3300</v>
       </c>
       <c r="D1545" t="inlineStr"/>
       <c r="E1545" t="inlineStr">
@@ -40059,16 +40059,16 @@
     <row r="1546">
       <c r="A1546" t="inlineStr">
         <is>
-          <t>380103</t>
+          <t>354301</t>
         </is>
       </c>
       <c r="B1546" t="inlineStr">
         <is>
-          <t>DIOXIDO DE TITANIO</t>
+          <t>AMIDET N</t>
         </is>
       </c>
       <c r="C1546" t="n">
-        <v>3300</v>
+        <v>17900</v>
       </c>
       <c r="D1546" t="inlineStr"/>
       <c r="E1546" t="inlineStr">
@@ -40345,42 +40345,42 @@
     <row r="1557">
       <c r="A1557" t="inlineStr">
         <is>
-          <t>250702</t>
+          <t>R030603</t>
         </is>
       </c>
       <c r="B1557" t="inlineStr">
         <is>
-          <t>250702</t>
+          <t>MINI UNGÜENTO 30ML</t>
         </is>
       </c>
       <c r="C1557" t="n">
-        <v>2350</v>
+        <v>2265</v>
       </c>
       <c r="D1557" t="inlineStr"/>
       <c r="E1557" t="inlineStr">
         <is>
-          <t>MATERIA PRIMA</t>
+          <t>PRODUCTO MANUFACTURADO</t>
         </is>
       </c>
       <c r="F1557" t="inlineStr">
         <is>
-          <t>Producción</t>
+          <t>Cuarentena</t>
         </is>
       </c>
     </row>
     <row r="1558">
       <c r="A1558" t="inlineStr">
         <is>
-          <t>344503</t>
+          <t>250702</t>
         </is>
       </c>
       <c r="B1558" t="inlineStr">
         <is>
-          <t>344503</t>
+          <t>250702</t>
         </is>
       </c>
       <c r="C1558" t="n">
-        <v>101280</v>
+        <v>2350</v>
       </c>
       <c r="D1558" t="inlineStr"/>
       <c r="E1558" t="inlineStr">
@@ -40397,26 +40397,26 @@
     <row r="1559">
       <c r="A1559" t="inlineStr">
         <is>
-          <t>R030603</t>
+          <t>344503</t>
         </is>
       </c>
       <c r="B1559" t="inlineStr">
         <is>
-          <t>MINI UNGÜENTO 30ML</t>
+          <t>344503</t>
         </is>
       </c>
       <c r="C1559" t="n">
-        <v>2265</v>
+        <v>101280</v>
       </c>
       <c r="D1559" t="inlineStr"/>
       <c r="E1559" t="inlineStr">
         <is>
-          <t>PRODUCTO MANUFACTURADO</t>
+          <t>MATERIA PRIMA</t>
         </is>
       </c>
       <c r="F1559" t="inlineStr">
         <is>
-          <t>Cuarentena</t>
+          <t>Producción</t>
         </is>
       </c>
     </row>
@@ -40871,21 +40871,21 @@
     <row r="1577">
       <c r="A1577" t="inlineStr">
         <is>
-          <t>144301</t>
+          <t>ET0204VG</t>
         </is>
       </c>
       <c r="B1577" t="inlineStr">
         <is>
-          <t>ALCOHOL CETOESTEARÍLICO 30/70</t>
+          <t>ETIQUETA LIP GLOSS VIVIANA GRONDONA D2</t>
         </is>
       </c>
       <c r="C1577" t="n">
-        <v>80950</v>
+        <v>2500</v>
       </c>
       <c r="D1577" t="inlineStr"/>
       <c r="E1577" t="inlineStr">
         <is>
-          <t>MATERIA PRIMA</t>
+          <t>MATERIAL DE ACONDICIONAMIENTO</t>
         </is>
       </c>
       <c r="F1577" t="inlineStr">
@@ -40897,12 +40897,12 @@
     <row r="1578">
       <c r="A1578" t="inlineStr">
         <is>
-          <t>ET0204VG</t>
+          <t>ET0203VG</t>
         </is>
       </c>
       <c r="B1578" t="inlineStr">
         <is>
-          <t>ETIQUETA LIP GLOSS VIVIANA GRONDONA D2</t>
+          <t>ETIQUETA LIP GLOSS VIVIANA GRONDONA D1</t>
         </is>
       </c>
       <c r="C1578" t="n">
@@ -40923,21 +40923,21 @@
     <row r="1579">
       <c r="A1579" t="inlineStr">
         <is>
-          <t>ET0203VG</t>
+          <t>144301</t>
         </is>
       </c>
       <c r="B1579" t="inlineStr">
         <is>
-          <t>ETIQUETA LIP GLOSS VIVIANA GRONDONA D1</t>
+          <t>ALCOHOL CETOESTEARÍLICO 30/70</t>
         </is>
       </c>
       <c r="C1579" t="n">
-        <v>2500</v>
+        <v>80950</v>
       </c>
       <c r="D1579" t="inlineStr"/>
       <c r="E1579" t="inlineStr">
         <is>
-          <t>MATERIAL DE ACONDICIONAMIENTO</t>
+          <t>MATERIA PRIMA</t>
         </is>
       </c>
       <c r="F1579" t="inlineStr">
@@ -41755,16 +41755,16 @@
     <row r="1611">
       <c r="A1611" t="inlineStr">
         <is>
-          <t>344001</t>
+          <t>370603</t>
         </is>
       </c>
       <c r="B1611" t="inlineStr">
         <is>
-          <t>344001</t>
+          <t>CLORURO DE SODIO</t>
         </is>
       </c>
       <c r="C1611" t="n">
-        <v>185</v>
+        <v>25340</v>
       </c>
       <c r="D1611" t="inlineStr"/>
       <c r="E1611" t="inlineStr">
@@ -41781,16 +41781,16 @@
     <row r="1612">
       <c r="A1612" t="inlineStr">
         <is>
-          <t>340108</t>
+          <t>344001</t>
         </is>
       </c>
       <c r="B1612" t="inlineStr">
         <is>
-          <t>WITARIX MCT</t>
+          <t>344001</t>
         </is>
       </c>
       <c r="C1612" t="n">
-        <v>23900</v>
+        <v>185</v>
       </c>
       <c r="D1612" t="inlineStr"/>
       <c r="E1612" t="inlineStr">
@@ -41807,16 +41807,16 @@
     <row r="1613">
       <c r="A1613" t="inlineStr">
         <is>
-          <t>370603</t>
+          <t>340108</t>
         </is>
       </c>
       <c r="B1613" t="inlineStr">
         <is>
-          <t>CLORURO DE SODIO</t>
+          <t>WITARIX MCT</t>
         </is>
       </c>
       <c r="C1613" t="n">
-        <v>25340</v>
+        <v>23900</v>
       </c>
       <c r="D1613" t="inlineStr"/>
       <c r="E1613" t="inlineStr">
@@ -43349,21 +43349,21 @@
     <row r="1672">
       <c r="A1672" t="inlineStr">
         <is>
-          <t>173501</t>
+          <t>ME1043</t>
         </is>
       </c>
       <c r="B1672" t="inlineStr">
         <is>
-          <t>ULTRAMAR U-200 AZUL</t>
+          <t>TAPA FLIP TOP DORADA ROSCA 18</t>
         </is>
       </c>
       <c r="C1672" t="n">
-        <v>1124</v>
+        <v>11319</v>
       </c>
       <c r="D1672" t="inlineStr"/>
       <c r="E1672" t="inlineStr">
         <is>
-          <t>MATERIA PRIMA</t>
+          <t>MATERIAL DE EMPAQUE</t>
         </is>
       </c>
       <c r="F1672" t="inlineStr">
@@ -43375,21 +43375,21 @@
     <row r="1673">
       <c r="A1673" t="inlineStr">
         <is>
-          <t>ME1043</t>
+          <t>173501</t>
         </is>
       </c>
       <c r="B1673" t="inlineStr">
         <is>
-          <t>TAPA FLIP TOP DORADA ROSCA 18</t>
+          <t>ULTRAMAR U-200 AZUL</t>
         </is>
       </c>
       <c r="C1673" t="n">
-        <v>11319</v>
+        <v>1124</v>
       </c>
       <c r="D1673" t="inlineStr"/>
       <c r="E1673" t="inlineStr">
         <is>
-          <t>MATERIAL DE EMPAQUE</t>
+          <t>MATERIA PRIMA</t>
         </is>
       </c>
       <c r="F1673" t="inlineStr">
@@ -47317,12 +47317,12 @@
     <row r="1828">
       <c r="A1828" t="inlineStr">
         <is>
-          <t>VB020101-01-01-S-19</t>
+          <t>VB020303-01-03-L-30</t>
         </is>
       </c>
       <c r="B1828" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-ANIMAL PRINT CAFÉ</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-L-PLUMAS</t>
         </is>
       </c>
       <c r="C1828" t="n">
@@ -47339,12 +47339,12 @@
     <row r="1829">
       <c r="A1829" t="inlineStr">
         <is>
-          <t>VB020303-01-03-L-30</t>
+          <t>VB020101-01-01-S-19</t>
         </is>
       </c>
       <c r="B1829" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-L-PLUMAS</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C1829" t="n">
@@ -47515,16 +47515,16 @@
     <row r="1837">
       <c r="A1837" t="inlineStr">
         <is>
-          <t>VB020303-01-01-S-30</t>
+          <t>VB020103-01-03-L-26</t>
         </is>
       </c>
       <c r="B1837" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-S-PLUMAS</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI-L-MISTICO</t>
         </is>
       </c>
       <c r="C1837" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D1837" t="inlineStr"/>
       <c r="E1837" t="inlineStr"/>
@@ -47537,16 +47537,16 @@
     <row r="1838">
       <c r="A1838" t="inlineStr">
         <is>
-          <t>VB020105-01-03-L-05</t>
+          <t>VB020303-01-02-M-30</t>
         </is>
       </c>
       <c r="B1838" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-L-AMARILLO NEON</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-M-PLUMAS</t>
         </is>
       </c>
       <c r="C1838" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1838" t="inlineStr"/>
       <c r="E1838" t="inlineStr"/>
@@ -47559,16 +47559,16 @@
     <row r="1839">
       <c r="A1839" t="inlineStr">
         <is>
-          <t>VB020103-03-01-S-20</t>
+          <t>VB020303-01-01-S-30</t>
         </is>
       </c>
       <c r="B1839" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-S-ANIMAL PRINT FLORES</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-S-PLUMAS</t>
         </is>
       </c>
       <c r="C1839" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D1839" t="inlineStr"/>
       <c r="E1839" t="inlineStr"/>
@@ -47581,16 +47581,16 @@
     <row r="1840">
       <c r="A1840" t="inlineStr">
         <is>
-          <t>VB020101-01-01-S-30</t>
+          <t>VB020105-01-03-L-05</t>
         </is>
       </c>
       <c r="B1840" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-PLUMAS</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-L-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C1840" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D1840" t="inlineStr"/>
       <c r="E1840" t="inlineStr"/>
@@ -47603,16 +47603,16 @@
     <row r="1841">
       <c r="A1841" t="inlineStr">
         <is>
-          <t>VB020101-01-03-L-19</t>
+          <t>VB020103-03-01-S-20</t>
         </is>
       </c>
       <c r="B1841" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-ANIMAL PRINT CAFÉ</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI BOLEROS-S-ANIMAL PRINT FLORES</t>
         </is>
       </c>
       <c r="C1841" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D1841" t="inlineStr"/>
       <c r="E1841" t="inlineStr"/>
@@ -47625,16 +47625,16 @@
     <row r="1842">
       <c r="A1842" t="inlineStr">
         <is>
-          <t>VB020101-01-02-M-14</t>
+          <t>VB020101-01-01-S-30</t>
         </is>
       </c>
       <c r="B1842" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-PALO DE ROSA</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-PLUMAS</t>
         </is>
       </c>
       <c r="C1842" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1842" t="inlineStr"/>
       <c r="E1842" t="inlineStr"/>
@@ -47647,12 +47647,12 @@
     <row r="1843">
       <c r="A1843" t="inlineStr">
         <is>
-          <t>VB020105-01-01-S-11</t>
+          <t>VB020101-01-03-L-19</t>
         </is>
       </c>
       <c r="B1843" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-S-FUCSIA NEON</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C1843" t="n">
@@ -47669,12 +47669,12 @@
     <row r="1844">
       <c r="A1844" t="inlineStr">
         <is>
-          <t>VB020103-01-03-L-26</t>
+          <t>VB020101-01-02-M-14</t>
         </is>
       </c>
       <c r="B1844" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI-L-MISTICO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-PALO DE ROSA</t>
         </is>
       </c>
       <c r="C1844" t="n">
@@ -47691,12 +47691,12 @@
     <row r="1845">
       <c r="A1845" t="inlineStr">
         <is>
-          <t>VB020303-01-02-M-30</t>
+          <t>VB020101-01-03-L-14</t>
         </is>
       </c>
       <c r="B1845" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-M-PLUMAS</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-PALO DE ROSA</t>
         </is>
       </c>
       <c r="C1845" t="n">
@@ -47713,16 +47713,16 @@
     <row r="1846">
       <c r="A1846" t="inlineStr">
         <is>
-          <t>VB020101-01-03-L-14</t>
+          <t>VB020103-01-01-S-26</t>
         </is>
       </c>
       <c r="B1846" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-PALO DE ROSA</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI-S-MISTICO</t>
         </is>
       </c>
       <c r="C1846" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D1846" t="inlineStr"/>
       <c r="E1846" t="inlineStr"/>
@@ -47735,16 +47735,16 @@
     <row r="1847">
       <c r="A1847" t="inlineStr">
         <is>
-          <t>VB020103-01-01-S-26</t>
+          <t>VB020105-01-01-S-11</t>
         </is>
       </c>
       <c r="B1847" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI-S-MISTICO</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-S-FUCSIA NEON</t>
         </is>
       </c>
       <c r="C1847" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1847" t="inlineStr"/>
       <c r="E1847" t="inlineStr"/>
@@ -47757,16 +47757,16 @@
     <row r="1848">
       <c r="A1848" t="inlineStr">
         <is>
-          <t>VB020105-01-03-L-15</t>
+          <t>VB020105-01-02-M-08</t>
         </is>
       </c>
       <c r="B1848" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-L-PURPURA</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-M-AZUL REY</t>
         </is>
       </c>
       <c r="C1848" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D1848" t="inlineStr"/>
       <c r="E1848" t="inlineStr"/>
@@ -47779,16 +47779,16 @@
     <row r="1849">
       <c r="A1849" t="inlineStr">
         <is>
-          <t>VB020105-01-02-M-08</t>
+          <t>VB020105-01-03-L-15</t>
         </is>
       </c>
       <c r="B1849" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-M-AZUL REY</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-L-PURPURA</t>
         </is>
       </c>
       <c r="C1849" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1849" t="inlineStr"/>
       <c r="E1849" t="inlineStr"/>
@@ -49605,16 +49605,16 @@
     <row r="1932">
       <c r="A1932" t="inlineStr">
         <is>
-          <t>VB0306-01-02-M-16</t>
+          <t>VB0302-01-02-M-02</t>
         </is>
       </c>
       <c r="B1932" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-M-ROJO</t>
+          <t>PANTALON ALTO-M-NEGRO</t>
         </is>
       </c>
       <c r="C1932" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D1932" t="inlineStr"/>
       <c r="E1932" t="inlineStr"/>
@@ -49627,16 +49627,16 @@
     <row r="1933">
       <c r="A1933" t="inlineStr">
         <is>
-          <t>VB0306-01-02-M-14</t>
+          <t>VB020203-01-02-M-01</t>
         </is>
       </c>
       <c r="B1933" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-M-PALO DE ROSA</t>
+          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-M-BLANCO</t>
         </is>
       </c>
       <c r="C1933" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D1933" t="inlineStr"/>
       <c r="E1933" t="inlineStr"/>
@@ -49649,16 +49649,16 @@
     <row r="1934">
       <c r="A1934" t="inlineStr">
         <is>
-          <t>VB0306-01-03-L-16</t>
+          <t>VB020203-01-03-L-01</t>
         </is>
       </c>
       <c r="B1934" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-L-ROJO</t>
+          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-L-BLANCO</t>
         </is>
       </c>
       <c r="C1934" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D1934" t="inlineStr"/>
       <c r="E1934" t="inlineStr"/>
@@ -49671,16 +49671,16 @@
     <row r="1935">
       <c r="A1935" t="inlineStr">
         <is>
-          <t>VB0306-01-03-L-14</t>
+          <t>VB0105-01-03-L-23</t>
         </is>
       </c>
       <c r="B1935" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-L-PALO DE ROSA</t>
+          <t>VB ENTERO TANGA-L-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C1935" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D1935" t="inlineStr"/>
       <c r="E1935" t="inlineStr"/>
@@ -49693,16 +49693,16 @@
     <row r="1936">
       <c r="A1936" t="inlineStr">
         <is>
-          <t>VB0306-01-01-S-16</t>
+          <t>VB020202-01-02-M-23</t>
         </is>
       </c>
       <c r="B1936" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-S-ROJO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-M-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C1936" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D1936" t="inlineStr"/>
       <c r="E1936" t="inlineStr"/>
@@ -49715,16 +49715,16 @@
     <row r="1937">
       <c r="A1937" t="inlineStr">
         <is>
-          <t>VB0306-01-01-S-14</t>
+          <t>VB020303-01-03-L-26</t>
         </is>
       </c>
       <c r="B1937" t="inlineStr">
         <is>
-          <t>TOP BÁSICO LUISA-S-PALO DE ROSA</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-L-MISTICO</t>
         </is>
       </c>
       <c r="C1937" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D1937" t="inlineStr"/>
       <c r="E1937" t="inlineStr"/>
@@ -49737,16 +49737,16 @@
     <row r="1938">
       <c r="A1938" t="inlineStr">
         <is>
-          <t>VB020101-01-03-L-16</t>
+          <t>VB020101-01-01-S-03</t>
         </is>
       </c>
       <c r="B1938" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-ROJO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-AGUAMARINA</t>
         </is>
       </c>
       <c r="C1938" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D1938" t="inlineStr"/>
       <c r="E1938" t="inlineStr"/>
@@ -49759,16 +49759,16 @@
     <row r="1939">
       <c r="A1939" t="inlineStr">
         <is>
-          <t>VB0103-01-03-L-16</t>
+          <t>VB020204-01-02-M-08</t>
         </is>
       </c>
       <c r="B1939" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-L-ROJO</t>
+          <t>VB DOS PIEZAS TOP PANTY-M-AZUL REY</t>
         </is>
       </c>
       <c r="C1939" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1939" t="inlineStr"/>
       <c r="E1939" t="inlineStr"/>
@@ -49781,19 +49781,23 @@
     <row r="1940">
       <c r="A1940" t="inlineStr">
         <is>
-          <t>VB020101-01-02-M-01</t>
+          <t>D051705</t>
         </is>
       </c>
       <c r="B1940" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-BLANCO</t>
+          <t>TERMO DLUCHI 450ML</t>
         </is>
       </c>
       <c r="C1940" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="D1940" t="inlineStr"/>
-      <c r="E1940" t="inlineStr"/>
+      <c r="E1940" t="inlineStr">
+        <is>
+          <t>PRODUCTO MANUFACTURADO</t>
+        </is>
+      </c>
       <c r="F1940" t="inlineStr">
         <is>
           <t>Cuarentena</t>
@@ -49803,16 +49807,16 @@
     <row r="1941">
       <c r="A1941" t="inlineStr">
         <is>
-          <t>VB0103-01-02-M-01</t>
+          <t>VB020204-01-01-S-15</t>
         </is>
       </c>
       <c r="B1941" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-M-BLANCO</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-PURPURA</t>
         </is>
       </c>
       <c r="C1941" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1941" t="inlineStr"/>
       <c r="E1941" t="inlineStr"/>
@@ -49825,12 +49829,12 @@
     <row r="1942">
       <c r="A1942" t="inlineStr">
         <is>
-          <t>VB020101-01-03-L-10</t>
+          <t>VB020303-01-02-M-26</t>
         </is>
       </c>
       <c r="B1942" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-FUCSIA</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-M-MISTICO</t>
         </is>
       </c>
       <c r="C1942" t="n">
@@ -49847,16 +49851,16 @@
     <row r="1943">
       <c r="A1943" t="inlineStr">
         <is>
-          <t>VB020101-01-03-L-02</t>
+          <t>VB020203-01-01-S-01</t>
         </is>
       </c>
       <c r="B1943" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-NEGRO</t>
+          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-S-BLANCO</t>
         </is>
       </c>
       <c r="C1943" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D1943" t="inlineStr"/>
       <c r="E1943" t="inlineStr"/>
@@ -49869,16 +49873,16 @@
     <row r="1944">
       <c r="A1944" t="inlineStr">
         <is>
-          <t>VB020101-01-01-S-02</t>
+          <t>VB020203-01-01-S-17</t>
         </is>
       </c>
       <c r="B1944" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-NEGRO</t>
+          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-S-ROSADO</t>
         </is>
       </c>
       <c r="C1944" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D1944" t="inlineStr"/>
       <c r="E1944" t="inlineStr"/>
@@ -49891,16 +49895,16 @@
     <row r="1945">
       <c r="A1945" t="inlineStr">
         <is>
-          <t>VB0103-01-01-S-02</t>
+          <t>VB020202-01-02-M-02</t>
         </is>
       </c>
       <c r="B1945" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-S-NEGRO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-M-NEGRO</t>
         </is>
       </c>
       <c r="C1945" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D1945" t="inlineStr"/>
       <c r="E1945" t="inlineStr"/>
@@ -49913,12 +49917,12 @@
     <row r="1946">
       <c r="A1946" t="inlineStr">
         <is>
-          <t>VB020101-01-03-L-07</t>
+          <t>VB020204-01-02-M-05</t>
         </is>
       </c>
       <c r="B1946" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-AZUL CIAN</t>
+          <t>VB DOS PIEZAS TOP PANTY-M-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C1946" t="n">
@@ -49935,16 +49939,16 @@
     <row r="1947">
       <c r="A1947" t="inlineStr">
         <is>
-          <t>VB020101-01-02-M-07</t>
+          <t>VB020105-01-01-S-01</t>
         </is>
       </c>
       <c r="B1947" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-AZUL CIAN</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-S-BLANCO</t>
         </is>
       </c>
       <c r="C1947" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1947" t="inlineStr"/>
       <c r="E1947" t="inlineStr"/>
@@ -49957,12 +49961,12 @@
     <row r="1948">
       <c r="A1948" t="inlineStr">
         <is>
-          <t>VB020101-01-03-L-01</t>
+          <t>VB020105-01-03-L-01</t>
         </is>
       </c>
       <c r="B1948" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-BLANCO</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-L-BLANCO</t>
         </is>
       </c>
       <c r="C1948" t="n">
@@ -49979,12 +49983,12 @@
     <row r="1949">
       <c r="A1949" t="inlineStr">
         <is>
-          <t>VB0103-01-03-L-01</t>
+          <t>VB020203-01-02-M-17</t>
         </is>
       </c>
       <c r="B1949" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-L-BLANCO</t>
+          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-M-ROSADO</t>
         </is>
       </c>
       <c r="C1949" t="n">
@@ -50001,16 +50005,16 @@
     <row r="1950">
       <c r="A1950" t="inlineStr">
         <is>
-          <t>VB020101-01-03-L-05</t>
+          <t>VB020202-01-01-S-02</t>
         </is>
       </c>
       <c r="B1950" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-AMARILLO NEON</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-S-NEGRO</t>
         </is>
       </c>
       <c r="C1950" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1950" t="inlineStr"/>
       <c r="E1950" t="inlineStr"/>
@@ -50023,12 +50027,12 @@
     <row r="1951">
       <c r="A1951" t="inlineStr">
         <is>
-          <t>VB020101-01-02-M-05</t>
+          <t>VB020202-01-03-L-02</t>
         </is>
       </c>
       <c r="B1951" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-AMARILLO NEON</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-L-NEGRO</t>
         </is>
       </c>
       <c r="C1951" t="n">
@@ -50045,16 +50049,16 @@
     <row r="1952">
       <c r="A1952" t="inlineStr">
         <is>
-          <t>VB0105-01-03-L-31</t>
+          <t>VB020101-01-03-L-15</t>
         </is>
       </c>
       <c r="B1952" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA-L-SAFARI</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-PURPURA</t>
         </is>
       </c>
       <c r="C1952" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D1952" t="inlineStr"/>
       <c r="E1952" t="inlineStr"/>
@@ -50067,16 +50071,16 @@
     <row r="1953">
       <c r="A1953" t="inlineStr">
         <is>
-          <t>VB020402-01-03-L-31</t>
+          <t>VB020204-01-01-S-07</t>
         </is>
       </c>
       <c r="B1953" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS BUSO TALLE ALTO-L-SAFARI</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-AZUL CIAN</t>
         </is>
       </c>
       <c r="C1953" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D1953" t="inlineStr"/>
       <c r="E1953" t="inlineStr"/>
@@ -50089,16 +50093,16 @@
     <row r="1954">
       <c r="A1954" t="inlineStr">
         <is>
-          <t>VB020101-01-02-M-08</t>
+          <t>VB020204-01-02-M-11</t>
         </is>
       </c>
       <c r="B1954" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-AZUL REY</t>
+          <t>VB DOS PIEZAS TOP PANTY-M-FUCSIA NEON</t>
         </is>
       </c>
       <c r="C1954" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D1954" t="inlineStr"/>
       <c r="E1954" t="inlineStr"/>
@@ -50111,12 +50115,12 @@
     <row r="1955">
       <c r="A1955" t="inlineStr">
         <is>
-          <t>VB020101-01-03-L-08</t>
+          <t>VB020204-01-02-M-13</t>
         </is>
       </c>
       <c r="B1955" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-AZUL REY</t>
+          <t>VB DOS PIEZAS TOP PANTY-M-NARANJA</t>
         </is>
       </c>
       <c r="C1955" t="n">
@@ -50133,12 +50137,12 @@
     <row r="1956">
       <c r="A1956" t="inlineStr">
         <is>
-          <t>VB0105-01-02-M-31</t>
+          <t>VB020103-02-03-L-03</t>
         </is>
       </c>
       <c r="B1956" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA-M-SAFARI</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-L-AGUAMARINA</t>
         </is>
       </c>
       <c r="C1956" t="n">
@@ -50155,16 +50159,16 @@
     <row r="1957">
       <c r="A1957" t="inlineStr">
         <is>
-          <t>VB020202-01-01-S-19</t>
+          <t>VB020103-02-02-M-03</t>
         </is>
       </c>
       <c r="B1957" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-S-ANIMAL PRINT CAFÉ</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-M-AGUAMARINA</t>
         </is>
       </c>
       <c r="C1957" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D1957" t="inlineStr"/>
       <c r="E1957" t="inlineStr"/>
@@ -50177,12 +50181,12 @@
     <row r="1958">
       <c r="A1958" t="inlineStr">
         <is>
-          <t>VB0103-01-01-S-01</t>
+          <t>VB020103-02-01-S-03</t>
         </is>
       </c>
       <c r="B1958" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-S-BLANCO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-S-AGUAMARINA</t>
         </is>
       </c>
       <c r="C1958" t="n">
@@ -50199,12 +50203,12 @@
     <row r="1959">
       <c r="A1959" t="inlineStr">
         <is>
-          <t>VB020101-01-02-M-16</t>
+          <t>VB020303-01-01-S-26</t>
         </is>
       </c>
       <c r="B1959" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-ROJO</t>
+          <t>VB DOS PIEZAS HALTER BIKINI-S-MISTICO</t>
         </is>
       </c>
       <c r="C1959" t="n">
@@ -50221,16 +50225,16 @@
     <row r="1960">
       <c r="A1960" t="inlineStr">
         <is>
-          <t>VB020101-01-03-L-17</t>
+          <t>VB020204-01-01-S-05</t>
         </is>
       </c>
       <c r="B1960" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-ROSADO</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C1960" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D1960" t="inlineStr"/>
       <c r="E1960" t="inlineStr"/>
@@ -50243,16 +50247,16 @@
     <row r="1961">
       <c r="A1961" t="inlineStr">
         <is>
-          <t>VB020101-01-02-M-17</t>
+          <t>VB020204-01-03-L-11</t>
         </is>
       </c>
       <c r="B1961" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-ROSADO</t>
+          <t>VB DOS PIEZAS TOP PANTY-L-FUCSIA NEON</t>
         </is>
       </c>
       <c r="C1961" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1961" t="inlineStr"/>
       <c r="E1961" t="inlineStr"/>
@@ -50265,16 +50269,16 @@
     <row r="1962">
       <c r="A1962" t="inlineStr">
         <is>
-          <t>VB020104-01-01-S-02</t>
+          <t>VB0105-01-02-M-23</t>
         </is>
       </c>
       <c r="B1962" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO PANTY-S-NEGRO</t>
+          <t>VB ENTERO TANGA-M-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C1962" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D1962" t="inlineStr"/>
       <c r="E1962" t="inlineStr"/>
@@ -50287,16 +50291,16 @@
     <row r="1963">
       <c r="A1963" t="inlineStr">
         <is>
-          <t>VB020205-03-02-M-21</t>
+          <t>VB0302-01-01-S-01</t>
         </is>
       </c>
       <c r="B1963" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-M-ASTRAL</t>
+          <t>PANTALON ALTO-S-BLANCO</t>
         </is>
       </c>
       <c r="C1963" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1963" t="inlineStr"/>
       <c r="E1963" t="inlineStr"/>
@@ -50309,16 +50313,16 @@
     <row r="1964">
       <c r="A1964" t="inlineStr">
         <is>
-          <t>VB020101-01-01-S-16</t>
+          <t>VB020103-02-03-L-17</t>
         </is>
       </c>
       <c r="B1964" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-ROJO</t>
+          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-L-ROSADO</t>
         </is>
       </c>
       <c r="C1964" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D1964" t="inlineStr"/>
       <c r="E1964" t="inlineStr"/>
@@ -50331,16 +50335,16 @@
     <row r="1965">
       <c r="A1965" t="inlineStr">
         <is>
-          <t>VB020205-03-01-S-21</t>
+          <t>VB020101-01-03-L-03</t>
         </is>
       </c>
       <c r="B1965" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-S-ASTRAL</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-AGUAMARINA</t>
         </is>
       </c>
       <c r="C1965" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D1965" t="inlineStr"/>
       <c r="E1965" t="inlineStr"/>
@@ -50353,16 +50357,16 @@
     <row r="1966">
       <c r="A1966" t="inlineStr">
         <is>
-          <t>VB020205-02-02-M-07</t>
+          <t>VB0105-01-01-S-23</t>
         </is>
       </c>
       <c r="B1966" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-M-AZUL CIAN</t>
+          <t>VB ENTERO TANGA-S-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C1966" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D1966" t="inlineStr"/>
       <c r="E1966" t="inlineStr"/>
@@ -50375,12 +50379,12 @@
     <row r="1967">
       <c r="A1967" t="inlineStr">
         <is>
-          <t>VB020205-02-02-M-04</t>
+          <t>VB020204-01-01-S-11</t>
         </is>
       </c>
       <c r="B1967" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-M-AMARILLO</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-FUCSIA NEON</t>
         </is>
       </c>
       <c r="C1967" t="n">
@@ -50397,12 +50401,12 @@
     <row r="1968">
       <c r="A1968" t="inlineStr">
         <is>
-          <t>VB020205-02-03-L-12</t>
+          <t>VB0302-01-03-L-02</t>
         </is>
       </c>
       <c r="B1968" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-L-MORADO</t>
+          <t>PANTALON ALTO-L-NEGRO</t>
         </is>
       </c>
       <c r="C1968" t="n">
@@ -50419,12 +50423,12 @@
     <row r="1969">
       <c r="A1969" t="inlineStr">
         <is>
-          <t>VB020205-02-03-L-10</t>
+          <t>VB020204-01-01-S-08</t>
         </is>
       </c>
       <c r="B1969" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-L-FUCSIA</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-AZUL REY</t>
         </is>
       </c>
       <c r="C1969" t="n">
@@ -50441,12 +50445,12 @@
     <row r="1970">
       <c r="A1970" t="inlineStr">
         <is>
-          <t>VB020205-02-03-L-22</t>
+          <t>VB020105-01-01-S-16</t>
         </is>
       </c>
       <c r="B1970" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-L-FLORES</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-S-ROJO</t>
         </is>
       </c>
       <c r="C1970" t="n">
@@ -50463,12 +50467,12 @@
     <row r="1971">
       <c r="A1971" t="inlineStr">
         <is>
-          <t>VB020205-02-03-L-07</t>
+          <t>VB020105-01-02-M-16</t>
         </is>
       </c>
       <c r="B1971" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-L-AZUL CIAN</t>
+          <t>VB DOS PIEZAS TRIANGULO TANGA-M-ROJO</t>
         </is>
       </c>
       <c r="C1971" t="n">
@@ -50485,16 +50489,16 @@
     <row r="1972">
       <c r="A1972" t="inlineStr">
         <is>
-          <t>VB020205-02-03-L-04</t>
+          <t>VB020203-01-03-L-02</t>
         </is>
       </c>
       <c r="B1972" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-L-AMARILLO</t>
+          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-L-NEGRO</t>
         </is>
       </c>
       <c r="C1972" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D1972" t="inlineStr"/>
       <c r="E1972" t="inlineStr"/>
@@ -50507,16 +50511,16 @@
     <row r="1973">
       <c r="A1973" t="inlineStr">
         <is>
-          <t>VB020205-03-03-L-21</t>
+          <t>VB0302-01-03-L-01</t>
         </is>
       </c>
       <c r="B1973" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-L-ASTRAL</t>
+          <t>PANTALON ALTO-L-BLANCO</t>
         </is>
       </c>
       <c r="C1973" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D1973" t="inlineStr"/>
       <c r="E1973" t="inlineStr"/>
@@ -50529,16 +50533,16 @@
     <row r="1974">
       <c r="A1974" t="inlineStr">
         <is>
-          <t>VB0105-01-01-S-31</t>
+          <t>VB020101-01-02-M-15</t>
         </is>
       </c>
       <c r="B1974" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA-S-SAFARI</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-PURPURA</t>
         </is>
       </c>
       <c r="C1974" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D1974" t="inlineStr"/>
       <c r="E1974" t="inlineStr"/>
@@ -50551,12 +50555,12 @@
     <row r="1975">
       <c r="A1975" t="inlineStr">
         <is>
-          <t>VB020202-01-01-S-08</t>
+          <t>VB020204-01-01-S-13</t>
         </is>
       </c>
       <c r="B1975" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-S-AZUL REY</t>
+          <t>VB DOS PIEZAS TOP PANTY-S-NARANJA</t>
         </is>
       </c>
       <c r="C1975" t="n">
@@ -50573,16 +50577,16 @@
     <row r="1976">
       <c r="A1976" t="inlineStr">
         <is>
-          <t>VB020202-01-01-S-04</t>
+          <t>VB020204-01-03-L-07</t>
         </is>
       </c>
       <c r="B1976" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-S-AMARILLO</t>
+          <t>VB DOS PIEZAS TOP PANTY-L-AZUL CIAN</t>
         </is>
       </c>
       <c r="C1976" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1976" t="inlineStr"/>
       <c r="E1976" t="inlineStr"/>
@@ -50595,12 +50599,12 @@
     <row r="1977">
       <c r="A1977" t="inlineStr">
         <is>
-          <t>VB020202-01-02-M-19</t>
+          <t>VB0103-01-01-S-32</t>
         </is>
       </c>
       <c r="B1977" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-M-ANIMAL PRINT CAFÉ</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-S-SELVA PAJAROS</t>
         </is>
       </c>
       <c r="C1977" t="n">
@@ -50617,16 +50621,16 @@
     <row r="1978">
       <c r="A1978" t="inlineStr">
         <is>
-          <t>VB020202-01-02-M-08</t>
+          <t>VB020204-01-03-L-15</t>
         </is>
       </c>
       <c r="B1978" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-M-AZUL REY</t>
+          <t>VB DOS PIEZAS TOP PANTY-L-PURPURA</t>
         </is>
       </c>
       <c r="C1978" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1978" t="inlineStr"/>
       <c r="E1978" t="inlineStr"/>
@@ -50639,16 +50643,16 @@
     <row r="1979">
       <c r="A1979" t="inlineStr">
         <is>
-          <t>VB020202-01-02-M-04</t>
+          <t>VB020202-01-03-L-23</t>
         </is>
       </c>
       <c r="B1979" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-M-AMARILLO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-L-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C1979" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1979" t="inlineStr"/>
       <c r="E1979" t="inlineStr"/>
@@ -50661,16 +50665,16 @@
     <row r="1980">
       <c r="A1980" t="inlineStr">
         <is>
-          <t>VB020202-01-03-L-19</t>
+          <t>VB0103-01-03-L-32</t>
         </is>
       </c>
       <c r="B1980" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-L-ANIMAL PRINT CAFÉ</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-L-SELVA PAJAROS</t>
         </is>
       </c>
       <c r="C1980" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D1980" t="inlineStr"/>
       <c r="E1980" t="inlineStr"/>
@@ -50683,12 +50687,12 @@
     <row r="1981">
       <c r="A1981" t="inlineStr">
         <is>
-          <t>VB020202-01-03-L-08</t>
+          <t>VB0302-01-01-S-02</t>
         </is>
       </c>
       <c r="B1981" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-L-AZUL REY</t>
+          <t>PANTALON ALTO-S-NEGRO</t>
         </is>
       </c>
       <c r="C1981" t="n">
@@ -50705,16 +50709,16 @@
     <row r="1982">
       <c r="A1982" t="inlineStr">
         <is>
-          <t>VB020202-01-03-L-04</t>
+          <t>VB020204-01-03-L-08</t>
         </is>
       </c>
       <c r="B1982" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-L-AMARILLO</t>
+          <t>VB DOS PIEZAS TOP PANTY-L-AZUL REY</t>
         </is>
       </c>
       <c r="C1982" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D1982" t="inlineStr"/>
       <c r="E1982" t="inlineStr"/>
@@ -50727,16 +50731,16 @@
     <row r="1983">
       <c r="A1983" t="inlineStr">
         <is>
-          <t>VB020205-02-01-S-12</t>
+          <t>VB0302-01-02-M-01</t>
         </is>
       </c>
       <c r="B1983" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-S-MORADO</t>
+          <t>PANTALON ALTO-M-BLANCO</t>
         </is>
       </c>
       <c r="C1983" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1983" t="inlineStr"/>
       <c r="E1983" t="inlineStr"/>
@@ -50749,16 +50753,16 @@
     <row r="1984">
       <c r="A1984" t="inlineStr">
         <is>
-          <t>VB020205-02-01-S-10</t>
+          <t>VB0103-01-02-M-32</t>
         </is>
       </c>
       <c r="B1984" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-S-FUCSIA</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-M-SELVA PAJAROS</t>
         </is>
       </c>
       <c r="C1984" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D1984" t="inlineStr"/>
       <c r="E1984" t="inlineStr"/>
@@ -50771,16 +50775,16 @@
     <row r="1985">
       <c r="A1985" t="inlineStr">
         <is>
-          <t>VB020205-02-01-S-22</t>
+          <t>VB020202-01-01-S-23</t>
         </is>
       </c>
       <c r="B1985" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-S-FLORES</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-S-HOJAS AZUL</t>
         </is>
       </c>
       <c r="C1985" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D1985" t="inlineStr"/>
       <c r="E1985" t="inlineStr"/>
@@ -50793,16 +50797,16 @@
     <row r="1986">
       <c r="A1986" t="inlineStr">
         <is>
-          <t>VB020205-02-01-S-07</t>
+          <t>VB0306-01-03-L-16</t>
         </is>
       </c>
       <c r="B1986" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-S-AZUL CIAN</t>
+          <t>TOP BÁSICO LUISA-L-ROJO</t>
         </is>
       </c>
       <c r="C1986" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D1986" t="inlineStr"/>
       <c r="E1986" t="inlineStr"/>
@@ -50815,16 +50819,16 @@
     <row r="1987">
       <c r="A1987" t="inlineStr">
         <is>
-          <t>VB020205-02-02-M-10</t>
+          <t>VB0306-01-01-S-14</t>
         </is>
       </c>
       <c r="B1987" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-M-FUCSIA</t>
+          <t>TOP BÁSICO LUISA-S-PALO DE ROSA</t>
         </is>
       </c>
       <c r="C1987" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D1987" t="inlineStr"/>
       <c r="E1987" t="inlineStr"/>
@@ -50837,16 +50841,16 @@
     <row r="1988">
       <c r="A1988" t="inlineStr">
         <is>
-          <t>VB020205-02-01-S-04</t>
+          <t>VB0306-01-02-M-14</t>
         </is>
       </c>
       <c r="B1988" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-S-AMARILLO</t>
+          <t>TOP BÁSICO LUISA-M-PALO DE ROSA</t>
         </is>
       </c>
       <c r="C1988" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D1988" t="inlineStr"/>
       <c r="E1988" t="inlineStr"/>
@@ -50859,16 +50863,16 @@
     <row r="1989">
       <c r="A1989" t="inlineStr">
         <is>
-          <t>VB020205-02-02-M-22</t>
+          <t>VB0306-01-01-S-16</t>
         </is>
       </c>
       <c r="B1989" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TANGA-M-FLORES</t>
+          <t>TOP BÁSICO LUISA-S-ROJO</t>
         </is>
       </c>
       <c r="C1989" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D1989" t="inlineStr"/>
       <c r="E1989" t="inlineStr"/>
@@ -50881,16 +50885,16 @@
     <row r="1990">
       <c r="A1990" t="inlineStr">
         <is>
-          <t>VB0302-01-02-M-02</t>
+          <t>VB0306-01-03-L-14</t>
         </is>
       </c>
       <c r="B1990" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-M-NEGRO</t>
+          <t>TOP BÁSICO LUISA-L-PALO DE ROSA</t>
         </is>
       </c>
       <c r="C1990" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D1990" t="inlineStr"/>
       <c r="E1990" t="inlineStr"/>
@@ -50903,16 +50907,16 @@
     <row r="1991">
       <c r="A1991" t="inlineStr">
         <is>
-          <t>VB020203-01-02-M-01</t>
+          <t>VB0306-01-02-M-16</t>
         </is>
       </c>
       <c r="B1991" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-M-BLANCO</t>
+          <t>TOP BÁSICO LUISA-M-ROJO</t>
         </is>
       </c>
       <c r="C1991" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D1991" t="inlineStr"/>
       <c r="E1991" t="inlineStr"/>
@@ -50925,16 +50929,16 @@
     <row r="1992">
       <c r="A1992" t="inlineStr">
         <is>
-          <t>VB020203-01-03-L-01</t>
+          <t>VB020101-01-03-L-07</t>
         </is>
       </c>
       <c r="B1992" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-L-BLANCO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-AZUL CIAN</t>
         </is>
       </c>
       <c r="C1992" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D1992" t="inlineStr"/>
       <c r="E1992" t="inlineStr"/>
@@ -50947,16 +50951,16 @@
     <row r="1993">
       <c r="A1993" t="inlineStr">
         <is>
-          <t>VB0105-01-03-L-23</t>
+          <t>VB020101-01-02-M-07</t>
         </is>
       </c>
       <c r="B1993" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA-L-HOJAS AZUL</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-AZUL CIAN</t>
         </is>
       </c>
       <c r="C1993" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D1993" t="inlineStr"/>
       <c r="E1993" t="inlineStr"/>
@@ -50969,16 +50973,16 @@
     <row r="1994">
       <c r="A1994" t="inlineStr">
         <is>
-          <t>VB020202-01-02-M-23</t>
+          <t>VB020101-01-03-L-01</t>
         </is>
       </c>
       <c r="B1994" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-M-HOJAS AZUL</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-BLANCO</t>
         </is>
       </c>
       <c r="C1994" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1994" t="inlineStr"/>
       <c r="E1994" t="inlineStr"/>
@@ -50991,12 +50995,12 @@
     <row r="1995">
       <c r="A1995" t="inlineStr">
         <is>
-          <t>VB020303-01-03-L-26</t>
+          <t>VB0103-01-03-L-01</t>
         </is>
       </c>
       <c r="B1995" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-L-MISTICO</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-L-BLANCO</t>
         </is>
       </c>
       <c r="C1995" t="n">
@@ -51013,12 +51017,12 @@
     <row r="1996">
       <c r="A1996" t="inlineStr">
         <is>
-          <t>VB020101-01-01-S-03</t>
+          <t>VB020101-01-02-M-01</t>
         </is>
       </c>
       <c r="B1996" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-AGUAMARINA</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-BLANCO</t>
         </is>
       </c>
       <c r="C1996" t="n">
@@ -51035,16 +51039,16 @@
     <row r="1997">
       <c r="A1997" t="inlineStr">
         <is>
-          <t>VB020204-01-02-M-08</t>
+          <t>VB0103-01-02-M-01</t>
         </is>
       </c>
       <c r="B1997" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-M-AZUL REY</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-M-BLANCO</t>
         </is>
       </c>
       <c r="C1997" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D1997" t="inlineStr"/>
       <c r="E1997" t="inlineStr"/>
@@ -51057,23 +51061,19 @@
     <row r="1998">
       <c r="A1998" t="inlineStr">
         <is>
-          <t>D051705</t>
+          <t>VB020101-01-03-L-10</t>
         </is>
       </c>
       <c r="B1998" t="inlineStr">
         <is>
-          <t>TERMO DLUCHI 450ML</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-FUCSIA</t>
         </is>
       </c>
       <c r="C1998" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="D1998" t="inlineStr"/>
-      <c r="E1998" t="inlineStr">
-        <is>
-          <t>PRODUCTO MANUFACTURADO</t>
-        </is>
-      </c>
+      <c r="E1998" t="inlineStr"/>
       <c r="F1998" t="inlineStr">
         <is>
           <t>Cuarentena</t>
@@ -51083,16 +51083,16 @@
     <row r="1999">
       <c r="A1999" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-15</t>
+          <t>VB020101-01-03-L-02</t>
         </is>
       </c>
       <c r="B1999" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-PURPURA</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-NEGRO</t>
         </is>
       </c>
       <c r="C1999" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1999" t="inlineStr"/>
       <c r="E1999" t="inlineStr"/>
@@ -51105,16 +51105,16 @@
     <row r="2000">
       <c r="A2000" t="inlineStr">
         <is>
-          <t>VB020303-01-02-M-26</t>
+          <t>VB020101-01-01-S-02</t>
         </is>
       </c>
       <c r="B2000" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-M-MISTICO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-NEGRO</t>
         </is>
       </c>
       <c r="C2000" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2000" t="inlineStr"/>
       <c r="E2000" t="inlineStr"/>
@@ -51127,16 +51127,16 @@
     <row r="2001">
       <c r="A2001" t="inlineStr">
         <is>
-          <t>VB020203-01-01-S-01</t>
+          <t>VB0103-01-01-S-02</t>
         </is>
       </c>
       <c r="B2001" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-S-BLANCO</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-S-NEGRO</t>
         </is>
       </c>
       <c r="C2001" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2001" t="inlineStr"/>
       <c r="E2001" t="inlineStr"/>
@@ -51149,12 +51149,12 @@
     <row r="2002">
       <c r="A2002" t="inlineStr">
         <is>
-          <t>VB020203-01-01-S-17</t>
+          <t>VB0103-01-01-S-01</t>
         </is>
       </c>
       <c r="B2002" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-S-ROSADO</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-S-BLANCO</t>
         </is>
       </c>
       <c r="C2002" t="n">
@@ -51171,16 +51171,16 @@
     <row r="2003">
       <c r="A2003" t="inlineStr">
         <is>
-          <t>VB020202-01-02-M-02</t>
+          <t>VB020101-01-03-L-16</t>
         </is>
       </c>
       <c r="B2003" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-M-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-ROJO</t>
         </is>
       </c>
       <c r="C2003" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D2003" t="inlineStr"/>
       <c r="E2003" t="inlineStr"/>
@@ -51193,16 +51193,16 @@
     <row r="2004">
       <c r="A2004" t="inlineStr">
         <is>
-          <t>VB020204-01-02-M-05</t>
+          <t>VB0103-01-03-L-16</t>
         </is>
       </c>
       <c r="B2004" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-M-AMARILLO NEON</t>
+          <t>VB ENTERO BIKINI ESCOTE ESPALDA-L-ROJO</t>
         </is>
       </c>
       <c r="C2004" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2004" t="inlineStr"/>
       <c r="E2004" t="inlineStr"/>
@@ -51215,16 +51215,16 @@
     <row r="2005">
       <c r="A2005" t="inlineStr">
         <is>
-          <t>VB020105-01-01-S-01</t>
+          <t>VB020101-01-03-L-17</t>
         </is>
       </c>
       <c r="B2005" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-S-BLANCO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-ROSADO</t>
         </is>
       </c>
       <c r="C2005" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2005" t="inlineStr"/>
       <c r="E2005" t="inlineStr"/>
@@ -51237,16 +51237,16 @@
     <row r="2006">
       <c r="A2006" t="inlineStr">
         <is>
-          <t>VB020105-01-03-L-01</t>
+          <t>VB020101-01-02-M-17</t>
         </is>
       </c>
       <c r="B2006" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-L-BLANCO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-ROSADO</t>
         </is>
       </c>
       <c r="C2006" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2006" t="inlineStr"/>
       <c r="E2006" t="inlineStr"/>
@@ -51259,16 +51259,16 @@
     <row r="2007">
       <c r="A2007" t="inlineStr">
         <is>
-          <t>VB020203-01-02-M-17</t>
+          <t>VB020104-01-01-S-02</t>
         </is>
       </c>
       <c r="B2007" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-M-ROSADO</t>
+          <t>VB DOS PIEZAS TRIANGULO PANTY-S-NEGRO</t>
         </is>
       </c>
       <c r="C2007" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2007" t="inlineStr"/>
       <c r="E2007" t="inlineStr"/>
@@ -51281,16 +51281,16 @@
     <row r="2008">
       <c r="A2008" t="inlineStr">
         <is>
-          <t>VB020202-01-01-S-02</t>
+          <t>VB020101-01-01-S-16</t>
         </is>
       </c>
       <c r="B2008" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-S-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-S-ROJO</t>
         </is>
       </c>
       <c r="C2008" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2008" t="inlineStr"/>
       <c r="E2008" t="inlineStr"/>
@@ -51303,16 +51303,16 @@
     <row r="2009">
       <c r="A2009" t="inlineStr">
         <is>
-          <t>VB020202-01-03-L-02</t>
+          <t>VB020101-01-02-M-16</t>
         </is>
       </c>
       <c r="B2009" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-L-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-ROJO</t>
         </is>
       </c>
       <c r="C2009" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2009" t="inlineStr"/>
       <c r="E2009" t="inlineStr"/>
@@ -51325,16 +51325,16 @@
     <row r="2010">
       <c r="A2010" t="inlineStr">
         <is>
-          <t>VB020204-01-02-M-11</t>
+          <t>VB020205-02-01-S-10</t>
         </is>
       </c>
       <c r="B2010" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-M-FUCSIA NEON</t>
+          <t>VB DOS PIEZAS TOP TANGA-S-FUCSIA</t>
         </is>
       </c>
       <c r="C2010" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2010" t="inlineStr"/>
       <c r="E2010" t="inlineStr"/>
@@ -51347,16 +51347,16 @@
     <row r="2011">
       <c r="A2011" t="inlineStr">
         <is>
-          <t>VB020204-01-02-M-13</t>
+          <t>VB020205-02-01-S-22</t>
         </is>
       </c>
       <c r="B2011" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-M-NARANJA</t>
+          <t>VB DOS PIEZAS TOP TANGA-S-FLORES</t>
         </is>
       </c>
       <c r="C2011" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2011" t="inlineStr"/>
       <c r="E2011" t="inlineStr"/>
@@ -51369,12 +51369,12 @@
     <row r="2012">
       <c r="A2012" t="inlineStr">
         <is>
-          <t>VB020101-01-03-L-15</t>
+          <t>VB020205-02-01-S-07</t>
         </is>
       </c>
       <c r="B2012" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-PURPURA</t>
+          <t>VB DOS PIEZAS TOP TANGA-S-AZUL CIAN</t>
         </is>
       </c>
       <c r="C2012" t="n">
@@ -51391,16 +51391,16 @@
     <row r="2013">
       <c r="A2013" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-07</t>
+          <t>VB020205-02-02-M-10</t>
         </is>
       </c>
       <c r="B2013" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-AZUL CIAN</t>
+          <t>VB DOS PIEZAS TOP TANGA-M-FUCSIA</t>
         </is>
       </c>
       <c r="C2013" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2013" t="inlineStr"/>
       <c r="E2013" t="inlineStr"/>
@@ -51413,16 +51413,16 @@
     <row r="2014">
       <c r="A2014" t="inlineStr">
         <is>
-          <t>VB020103-02-02-M-03</t>
+          <t>VB020205-02-01-S-04</t>
         </is>
       </c>
       <c r="B2014" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-M-AGUAMARINA</t>
+          <t>VB DOS PIEZAS TOP TANGA-S-AMARILLO</t>
         </is>
       </c>
       <c r="C2014" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2014" t="inlineStr"/>
       <c r="E2014" t="inlineStr"/>
@@ -51435,12 +51435,12 @@
     <row r="2015">
       <c r="A2015" t="inlineStr">
         <is>
-          <t>VB020103-02-01-S-03</t>
+          <t>VB020205-02-02-M-22</t>
         </is>
       </c>
       <c r="B2015" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-S-AGUAMARINA</t>
+          <t>VB DOS PIEZAS TOP TANGA-M-FLORES</t>
         </is>
       </c>
       <c r="C2015" t="n">
@@ -51457,16 +51457,16 @@
     <row r="2016">
       <c r="A2016" t="inlineStr">
         <is>
-          <t>VB020103-02-03-L-03</t>
+          <t>VB020205-02-02-M-07</t>
         </is>
       </c>
       <c r="B2016" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-L-AGUAMARINA</t>
+          <t>VB DOS PIEZAS TOP TANGA-M-AZUL CIAN</t>
         </is>
       </c>
       <c r="C2016" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2016" t="inlineStr"/>
       <c r="E2016" t="inlineStr"/>
@@ -51479,16 +51479,16 @@
     <row r="2017">
       <c r="A2017" t="inlineStr">
         <is>
-          <t>VB020204-01-03-L-11</t>
+          <t>VB020205-02-02-M-04</t>
         </is>
       </c>
       <c r="B2017" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-L-FUCSIA NEON</t>
+          <t>VB DOS PIEZAS TOP TANGA-M-AMARILLO</t>
         </is>
       </c>
       <c r="C2017" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2017" t="inlineStr"/>
       <c r="E2017" t="inlineStr"/>
@@ -51501,16 +51501,16 @@
     <row r="2018">
       <c r="A2018" t="inlineStr">
         <is>
-          <t>VB0105-01-02-M-23</t>
+          <t>VB020205-02-03-L-12</t>
         </is>
       </c>
       <c r="B2018" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA-M-HOJAS AZUL</t>
+          <t>VB DOS PIEZAS TOP TANGA-L-MORADO</t>
         </is>
       </c>
       <c r="C2018" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2018" t="inlineStr"/>
       <c r="E2018" t="inlineStr"/>
@@ -51523,12 +51523,12 @@
     <row r="2019">
       <c r="A2019" t="inlineStr">
         <is>
-          <t>VB0302-01-01-S-01</t>
+          <t>VB020205-02-03-L-10</t>
         </is>
       </c>
       <c r="B2019" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-S-BLANCO</t>
+          <t>VB DOS PIEZAS TOP TANGA-L-FUCSIA</t>
         </is>
       </c>
       <c r="C2019" t="n">
@@ -51545,12 +51545,12 @@
     <row r="2020">
       <c r="A2020" t="inlineStr">
         <is>
-          <t>VB020105-01-01-S-16</t>
+          <t>VB020205-02-03-L-22</t>
         </is>
       </c>
       <c r="B2020" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-S-ROJO</t>
+          <t>VB DOS PIEZAS TOP TANGA-L-FLORES</t>
         </is>
       </c>
       <c r="C2020" t="n">
@@ -51567,12 +51567,12 @@
     <row r="2021">
       <c r="A2021" t="inlineStr">
         <is>
-          <t>VB020105-01-02-M-16</t>
+          <t>VB020205-02-03-L-07</t>
         </is>
       </c>
       <c r="B2021" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO TANGA-M-ROJO</t>
+          <t>VB DOS PIEZAS TOP TANGA-L-AZUL CIAN</t>
         </is>
       </c>
       <c r="C2021" t="n">
@@ -51589,16 +51589,16 @@
     <row r="2022">
       <c r="A2022" t="inlineStr">
         <is>
-          <t>VB020203-01-03-L-02</t>
+          <t>VB020205-02-03-L-04</t>
         </is>
       </c>
       <c r="B2022" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP BIKINI NIDO DE ABEJA-L-NEGRO</t>
+          <t>VB DOS PIEZAS TOP TANGA-L-AMARILLO</t>
         </is>
       </c>
       <c r="C2022" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2022" t="inlineStr"/>
       <c r="E2022" t="inlineStr"/>
@@ -51611,16 +51611,16 @@
     <row r="2023">
       <c r="A2023" t="inlineStr">
         <is>
-          <t>VB0302-01-03-L-01</t>
+          <t>VB020205-03-03-L-21</t>
         </is>
       </c>
       <c r="B2023" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-L-BLANCO</t>
+          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-L-ASTRAL</t>
         </is>
       </c>
       <c r="C2023" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2023" t="inlineStr"/>
       <c r="E2023" t="inlineStr"/>
@@ -51633,12 +51633,12 @@
     <row r="2024">
       <c r="A2024" t="inlineStr">
         <is>
-          <t>VB020204-01-03-L-15</t>
+          <t>VB020205-03-02-M-21</t>
         </is>
       </c>
       <c r="B2024" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-L-PURPURA</t>
+          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-M-ASTRAL</t>
         </is>
       </c>
       <c r="C2024" t="n">
@@ -51655,16 +51655,16 @@
     <row r="2025">
       <c r="A2025" t="inlineStr">
         <is>
-          <t>VB020202-01-03-L-23</t>
+          <t>VB020205-03-01-S-21</t>
         </is>
       </c>
       <c r="B2025" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-L-HOJAS AZUL</t>
+          <t>VB DOS PIEZAS TOP TANGA ORIFICIO-S-ASTRAL</t>
         </is>
       </c>
       <c r="C2025" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2025" t="inlineStr"/>
       <c r="E2025" t="inlineStr"/>
@@ -51677,16 +51677,16 @@
     <row r="2026">
       <c r="A2026" t="inlineStr">
         <is>
-          <t>VB0103-01-03-L-32</t>
+          <t>VB020101-01-03-L-05</t>
         </is>
       </c>
       <c r="B2026" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-L-SELVA PAJAROS</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C2026" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2026" t="inlineStr"/>
       <c r="E2026" t="inlineStr"/>
@@ -51699,12 +51699,12 @@
     <row r="2027">
       <c r="A2027" t="inlineStr">
         <is>
-          <t>VB0302-01-01-S-02</t>
+          <t>VB020101-01-02-M-05</t>
         </is>
       </c>
       <c r="B2027" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-S-NEGRO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-AMARILLO NEON</t>
         </is>
       </c>
       <c r="C2027" t="n">
@@ -51721,12 +51721,12 @@
     <row r="2028">
       <c r="A2028" t="inlineStr">
         <is>
-          <t>VB020204-01-03-L-08</t>
+          <t>VB020402-01-03-L-31</t>
         </is>
       </c>
       <c r="B2028" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-L-AZUL REY</t>
+          <t>VB DOS PIEZAS BUSO TALLE ALTO-L-SAFARI</t>
         </is>
       </c>
       <c r="C2028" t="n">
@@ -51743,16 +51743,16 @@
     <row r="2029">
       <c r="A2029" t="inlineStr">
         <is>
-          <t>VB0302-01-02-M-01</t>
+          <t>VB020101-01-02-M-08</t>
         </is>
       </c>
       <c r="B2029" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-M-BLANCO</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-AZUL REY</t>
         </is>
       </c>
       <c r="C2029" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2029" t="inlineStr"/>
       <c r="E2029" t="inlineStr"/>
@@ -51765,16 +51765,16 @@
     <row r="2030">
       <c r="A2030" t="inlineStr">
         <is>
-          <t>VB0103-01-02-M-32</t>
+          <t>VB020101-01-03-L-08</t>
         </is>
       </c>
       <c r="B2030" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-M-SELVA PAJAROS</t>
+          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-AZUL REY</t>
         </is>
       </c>
       <c r="C2030" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2030" t="inlineStr"/>
       <c r="E2030" t="inlineStr"/>
@@ -51787,12 +51787,12 @@
     <row r="2031">
       <c r="A2031" t="inlineStr">
         <is>
-          <t>VB020202-01-01-S-23</t>
+          <t>VB0105-01-03-L-31</t>
         </is>
       </c>
       <c r="B2031" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP TALLE ALTO-S-HOJAS AZUL</t>
+          <t>VB ENTERO TANGA-L-SAFARI</t>
         </is>
       </c>
       <c r="C2031" t="n">
@@ -51809,16 +51809,16 @@
     <row r="2032">
       <c r="A2032" t="inlineStr">
         <is>
-          <t>VB020101-01-02-M-15</t>
+          <t>VB0105-01-02-M-31</t>
         </is>
       </c>
       <c r="B2032" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-M-PURPURA</t>
+          <t>VB ENTERO TANGA-M-SAFARI</t>
         </is>
       </c>
       <c r="C2032" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D2032" t="inlineStr"/>
       <c r="E2032" t="inlineStr"/>
@@ -51831,16 +51831,16 @@
     <row r="2033">
       <c r="A2033" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-13</t>
+          <t>VB0105-01-01-S-31</t>
         </is>
       </c>
       <c r="B2033" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-NARANJA</t>
+          <t>VB ENTERO TANGA-S-SAFARI</t>
         </is>
       </c>
       <c r="C2033" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D2033" t="inlineStr"/>
       <c r="E2033" t="inlineStr"/>
@@ -51853,16 +51853,16 @@
     <row r="2034">
       <c r="A2034" t="inlineStr">
         <is>
-          <t>VB020204-01-03-L-07</t>
+          <t>VB020202-01-01-S-19</t>
         </is>
       </c>
       <c r="B2034" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-L-AZUL CIAN</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-S-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C2034" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2034" t="inlineStr"/>
       <c r="E2034" t="inlineStr"/>
@@ -51875,16 +51875,16 @@
     <row r="2035">
       <c r="A2035" t="inlineStr">
         <is>
-          <t>VB0103-01-01-S-32</t>
+          <t>VB020202-01-01-S-08</t>
         </is>
       </c>
       <c r="B2035" t="inlineStr">
         <is>
-          <t>VB ENTERO BIKINI ESCOTE ESPALDA-S-SELVA PAJAROS</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-S-AZUL REY</t>
         </is>
       </c>
       <c r="C2035" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2035" t="inlineStr"/>
       <c r="E2035" t="inlineStr"/>
@@ -51897,12 +51897,12 @@
     <row r="2036">
       <c r="A2036" t="inlineStr">
         <is>
-          <t>VB020103-02-03-L-17</t>
+          <t>VB020202-01-01-S-04</t>
         </is>
       </c>
       <c r="B2036" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO BIKINI NIDOABEJA-L-ROSADO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-S-AMARILLO</t>
         </is>
       </c>
       <c r="C2036" t="n">
@@ -51919,12 +51919,12 @@
     <row r="2037">
       <c r="A2037" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-05</t>
+          <t>VB020202-01-02-M-19</t>
         </is>
       </c>
       <c r="B2037" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-AMARILLO NEON</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-M-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C2037" t="n">
@@ -51941,16 +51941,16 @@
     <row r="2038">
       <c r="A2038" t="inlineStr">
         <is>
-          <t>VB020303-01-01-S-26</t>
+          <t>VB020202-01-02-M-08</t>
         </is>
       </c>
       <c r="B2038" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS HALTER BIKINI-S-MISTICO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-M-AZUL REY</t>
         </is>
       </c>
       <c r="C2038" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2038" t="inlineStr"/>
       <c r="E2038" t="inlineStr"/>
@@ -51963,12 +51963,12 @@
     <row r="2039">
       <c r="A2039" t="inlineStr">
         <is>
-          <t>VB020101-01-03-L-03</t>
+          <t>VB020202-01-02-M-04</t>
         </is>
       </c>
       <c r="B2039" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TRIANGULO ASOLEADOR-L-AGUAMARINA</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-M-AMARILLO</t>
         </is>
       </c>
       <c r="C2039" t="n">
@@ -51985,12 +51985,12 @@
     <row r="2040">
       <c r="A2040" t="inlineStr">
         <is>
-          <t>VB0105-01-01-S-23</t>
+          <t>VB020202-01-03-L-19</t>
         </is>
       </c>
       <c r="B2040" t="inlineStr">
         <is>
-          <t>VB ENTERO TANGA-S-HOJAS AZUL</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-L-ANIMAL PRINT CAFÉ</t>
         </is>
       </c>
       <c r="C2040" t="n">
@@ -52007,16 +52007,16 @@
     <row r="2041">
       <c r="A2041" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-11</t>
+          <t>VB020202-01-03-L-08</t>
         </is>
       </c>
       <c r="B2041" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-FUCSIA NEON</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-L-AZUL REY</t>
         </is>
       </c>
       <c r="C2041" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2041" t="inlineStr"/>
       <c r="E2041" t="inlineStr"/>
@@ -52029,16 +52029,16 @@
     <row r="2042">
       <c r="A2042" t="inlineStr">
         <is>
-          <t>VB0302-01-03-L-02</t>
+          <t>VB020202-01-03-L-04</t>
         </is>
       </c>
       <c r="B2042" t="inlineStr">
         <is>
-          <t>PANTALON ALTO-L-NEGRO</t>
+          <t>VB DOS PIEZAS TOP TALLE ALTO-L-AMARILLO</t>
         </is>
       </c>
       <c r="C2042" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2042" t="inlineStr"/>
       <c r="E2042" t="inlineStr"/>
@@ -52051,16 +52051,16 @@
     <row r="2043">
       <c r="A2043" t="inlineStr">
         <is>
-          <t>VB020204-01-01-S-08</t>
+          <t>VB020205-02-01-S-12</t>
         </is>
       </c>
       <c r="B2043" t="inlineStr">
         <is>
-          <t>VB DOS PIEZAS TOP PANTY-S-AZUL REY</t>
+          <t>VB DOS PIEZAS TOP TANGA-S-MORADO</t>
         </is>
       </c>
       <c r="C2043" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2043" t="inlineStr"/>
       <c r="E2043" t="inlineStr"/>
